--- a/1740CAF.xlsx
+++ b/1740CAF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lan74_pitt_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27FB8761-EB97-44C5-B2A5-9BD24A1DD465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2978696C-1EE7-48BA-AA78-26FBAA5F5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="760" windowWidth="23260" windowHeight="16260" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
+    <workbookView xWindow="5540" yWindow="760" windowWidth="23260" windowHeight="16260" firstSheet="2" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
   <sheets>
     <sheet name="2015-Present" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="364">
   <si>
     <t>Year</t>
   </si>
@@ -58,18 +58,18 @@
     <t>Organization/Applicant</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Additional Notes</t>
+  </si>
+  <si>
     <t>Location/Municipality</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Additional Notes</t>
-  </si>
-  <si>
     <t>support Carnegie Science Center Future Cities Competition</t>
   </si>
   <si>
@@ -79,12 +79,12 @@
     <t>Carnegie Science Center future cities program</t>
   </si>
   <si>
+    <t>to support the Carnegie Science Center Future Cities Competition ($2,000 per year for 2015 and 2016</t>
+  </si>
+  <si>
     <t>North Shore City; Pitt</t>
   </si>
   <si>
-    <t>to support the Carnegie Science Center Future Cities Competition ($2,000 per year for 2015 and 2016</t>
-  </si>
-  <si>
     <t>planting trees</t>
   </si>
   <si>
@@ -94,18 +94,15 @@
     <t>Tree Pittsburgh</t>
   </si>
   <si>
+    <t xml:space="preserve"> to plant trees on industrial properties in Lawrenceville, Chateau, and Neville Island; requested by Tree Pittsburgh</t>
+  </si>
+  <si>
     <t>Lawrenceville, Chateau, and Neville Island</t>
   </si>
   <si>
-    <t xml:space="preserve"> to plant trees on industrial properties in Lawrenceville, Chateau, and Neville Island; requested by Tree Pittsburgh</t>
-  </si>
-  <si>
     <t>discourage open burning and educate on the health effects of wood smoke</t>
   </si>
   <si>
-    <t>Education/Campaign</t>
-  </si>
-  <si>
     <t>Outreach Campaign</t>
   </si>
   <si>
@@ -127,21 +124,21 @@
     <t>purchase of solar panels to light parking lots and charge electric vehicles at CCAC campuses</t>
   </si>
   <si>
-    <t>Emission Reduction/Electric Vehicles/Solar</t>
+    <t>Emission Reduction, Diesel Reduction/Electrification</t>
   </si>
   <si>
     <t>Solar Panels</t>
   </si>
   <si>
+    <t>for the purchase of solar panels to light parking lots and charge electric vehicles at CCAC campuses</t>
+  </si>
+  <si>
+    <t>2 Categories</t>
+  </si>
+  <si>
     <t>Allegheny County</t>
   </si>
   <si>
-    <t>for the purchase of solar panels to light parking lots and charge electric vehicles at CCAC campuses</t>
-  </si>
-  <si>
-    <t>2 Categories</t>
-  </si>
-  <si>
     <t>fund 50% of an investment-grade audit for renovation of Clack Building #1</t>
   </si>
   <si>
@@ -157,117 +154,108 @@
     <t>fund six Student Conservation Association interns</t>
   </si>
   <si>
+    <t>Student Conservation Association</t>
+  </si>
+  <si>
+    <t>to fund six Student Conservation Association interns for city and county-based climate change group</t>
+  </si>
+  <si>
+    <t>fund a CMU air pollution modeling project</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>CMU Air Pollution</t>
+  </si>
+  <si>
+    <t>to fund a CMU air pollution modeling project aimed at predicting pollution dispersion in the Mon Valley and understanding air quality under multiple meteorological conditions and emissions scenarios</t>
+  </si>
+  <si>
+    <t>Mon Valley</t>
+  </si>
+  <si>
+    <t>funding for promoting residential solar energy options and contacts for contractors</t>
+  </si>
+  <si>
+    <t>Emission Reduction</t>
+  </si>
+  <si>
+    <t>Solarize Allegheny</t>
+  </si>
+  <si>
+    <t>to fund Solarize Allegheny, a project promoting residential solar energy options and contacts for contractors; project managed by SmartPower, a national non-profit marketing firm for clean energy</t>
+  </si>
+  <si>
+    <t>support for the ACHD project incentivizing owners of indoor fireplaces to convert to natural gas</t>
+  </si>
+  <si>
+    <t>ACHD Project</t>
+  </si>
+  <si>
+    <t>support for the ACHD project incentivizing owners of indoor fireplaces to convert to natural gas instead of burning wood (vendors would receive a rebate and purchasers would get a reduced price)</t>
+  </si>
+  <si>
+    <t>support the Southwest Pennsylvania Air Quality Partnership Lawnmower Exchange Program</t>
+  </si>
+  <si>
+    <t>Diesel Reduction/Electrification</t>
+  </si>
+  <si>
+    <t>Southwest Pennsylvania Air Quality</t>
+  </si>
+  <si>
+    <t>to support the Southwest Pennsylvania Air Quality Partnership Lawnmower Exchange Program ($12,000 per year for two years)</t>
+  </si>
+  <si>
+    <t>support the Carnegie Science Center Future Cities Competition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education/Competition </t>
+  </si>
+  <si>
+    <t>Carnegie Science Center fair</t>
+  </si>
+  <si>
+    <t>to support the Carnegie Science Center Future Cities Competition ($2,000 per year for the school years 2016-2017 and 2017-2018)</t>
+  </si>
+  <si>
+    <t>Pittsburgh</t>
+  </si>
+  <si>
+    <t>generate air quality awareness and community capacity in high priority areas</t>
+  </si>
+  <si>
+    <t>Public Communications</t>
+  </si>
+  <si>
+    <t>Air Space</t>
+  </si>
+  <si>
+    <t>to launch a new initiative ("Air-Space") to generate air quality awareness and community capacity in high priority areas throughout the County; requested by G-tech, which will partner with ACHD</t>
+  </si>
+  <si>
+    <t>Pittsburgh Regional Science &amp; Engineering Fair</t>
+  </si>
+  <si>
+    <t>Pittsburgh Regional Science Fair</t>
+  </si>
+  <si>
+    <t>to support the Pittsburgh Regional Science &amp; Engineering Fair ($2,500 per year for 2017, 2018, and 2019)</t>
+  </si>
+  <si>
+    <t>placing five Student Conservation Association Sustainability Fellows in environmental organizations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Conservation Association </t>
+  </si>
+  <si>
+    <t>to support placing five Student Conservation Association Sustainability Fellows in environmental organizations</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
-    <t>Student Conservation Association</t>
-  </si>
-  <si>
-    <t>to fund six Student Conservation Association interns for city and county-based climate change group</t>
-  </si>
-  <si>
-    <t>Employment ??</t>
-  </si>
-  <si>
-    <t>fund a CMU air pollution modeling project</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>CMU Air Pollution</t>
-  </si>
-  <si>
-    <t>Mon Valley</t>
-  </si>
-  <si>
-    <t>to fund a CMU air pollution modeling project aimed at predicting pollution dispersion in the Mon Valley and understanding air quality under multiple meteorological conditions and emissions scenarios</t>
-  </si>
-  <si>
-    <t>funding for promoting residential solar energy options and contacts for contractors</t>
-  </si>
-  <si>
-    <t>Emission Reduction/Solar</t>
-  </si>
-  <si>
-    <t>Solarize Allegheny</t>
-  </si>
-  <si>
-    <t>to fund Solarize Allegheny, a project promoting residential solar energy options and contacts for contractors; project managed by SmartPower, a national non-profit marketing firm for clean energy</t>
-  </si>
-  <si>
-    <t>support for the ACHD project incentivizing owners of indoor fireplaces to convert to natural gas</t>
-  </si>
-  <si>
-    <t>Emission Reduction</t>
-  </si>
-  <si>
-    <t>ACHD Project</t>
-  </si>
-  <si>
-    <t>support for the ACHD project incentivizing owners of indoor fireplaces to convert to natural gas instead of burning wood (vendors would receive a rebate and purchasers would get a reduced price)</t>
-  </si>
-  <si>
-    <t>support the Southwest Pennsylvania Air Quality Partnership Lawnmower Exchange Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diesel Reduction </t>
-  </si>
-  <si>
-    <t>Southwest Pennsylvania Air Quality</t>
-  </si>
-  <si>
-    <t>to support the Southwest Pennsylvania Air Quality Partnership Lawnmower Exchange Program ($12,000 per year for two years)</t>
-  </si>
-  <si>
-    <t>Ask about lawnmowers (are they electric)</t>
-  </si>
-  <si>
-    <t>support the Carnegie Science Center Future Cities Competition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education/Competition </t>
-  </si>
-  <si>
-    <t>Carnegie Science Center fair</t>
-  </si>
-  <si>
-    <t>Pittsburgh</t>
-  </si>
-  <si>
-    <t>to support the Carnegie Science Center Future Cities Competition ($2,000 per year for the school years 2016-2017 and 2017-2018)</t>
-  </si>
-  <si>
-    <t>generate air quality awareness and community capacity in high priority areas</t>
-  </si>
-  <si>
-    <t>Education/Public Communications</t>
-  </si>
-  <si>
-    <t>Air Space</t>
-  </si>
-  <si>
-    <t>to launch a new initiative ("Air-Space") to generate air quality awareness and community capacity in high priority areas throughout the County; requested by G-tech, which will partner with ACHD</t>
-  </si>
-  <si>
-    <t>Pittsburgh Regional Science &amp; Engineering Fair</t>
-  </si>
-  <si>
-    <t>Pittsburgh Regional Science Fair</t>
-  </si>
-  <si>
-    <t>to support the Pittsburgh Regional Science &amp; Engineering Fair ($2,500 per year for 2017, 2018, and 2019)</t>
-  </si>
-  <si>
-    <t>placing five Student Conservation Association Sustainability Fellows in environmental organizations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Conservation Association </t>
-  </si>
-  <si>
-    <t>to support placing five Student Conservation Association Sustainability Fellows in environmental organizations</t>
-  </si>
-  <si>
     <t>software to assist in tracking all aspects of asbestos renovation and demolition activities and stationary source enforcement</t>
   </si>
   <si>
@@ -280,7 +268,7 @@
     <t>air pollution public education projects and emission reduction projects</t>
   </si>
   <si>
-    <t>Education/Emission Reduction</t>
+    <t>Public Communication, Emission Reduction</t>
   </si>
   <si>
     <t>to fund small projects ($10k - $30k) addressing air pollution public education projects and emission reduction projects, with $150,000 going to each of the two categories</t>
@@ -316,7 +304,7 @@
     <t>for the Air Quality Program to run a half-day workshop for municipal officials on air quality topics</t>
   </si>
   <si>
-    <t>Operational Funding/Research ?</t>
+    <t>Operational Funding, Public Communication</t>
   </si>
   <si>
     <t>To provide professional and technical support on an as-needed basis to the Air Quality Program for case analysis, data and technical support, legal support, and medical and toxicology consulting</t>
@@ -346,12 +334,12 @@
     <t>County Department of Public Works</t>
   </si>
   <si>
+    <t>County Department of Public Works: for solar lighting along Corrigan Dr. in South Park</t>
+  </si>
+  <si>
     <t>Along Corrigan Dr. in South Park</t>
   </si>
   <si>
-    <t>County Department of Public Works: for solar lighting along Corrigan Dr. in South Park</t>
-  </si>
-  <si>
     <t>to support the Southwest Pennsylvania Air Quality Partnership lawnmower exchange program</t>
   </si>
   <si>
@@ -382,6 +370,9 @@
     <t>To update / develop software the Air Quality Program enforcement and permitting staff use</t>
   </si>
   <si>
+    <t>Operational Funding, Software</t>
+  </si>
+  <si>
     <t>Tree planting</t>
   </si>
   <si>
@@ -400,9 +391,6 @@
     <t>Air Quality Program 5% operations funding allocation for the year 2021</t>
   </si>
   <si>
-    <t>Operational Funding/Public Comm</t>
-  </si>
-  <si>
     <t>Air Quality  Program</t>
   </si>
   <si>
@@ -424,7 +412,7 @@
     <t>One Tree Per Child</t>
   </si>
   <si>
-    <t>Tree Planting/Education</t>
+    <t>Tree Planting, Education/Competition</t>
   </si>
   <si>
     <t>Project is ongoing, they have planted around 1,000 trees and engaged with the community</t>
@@ -490,34 +478,34 @@
     <t>Southwest Pennsylvania Air Quality Partnership</t>
   </si>
   <si>
+    <t>Support was provided for public outreach</t>
+  </si>
+  <si>
+    <t>Provide guidelines for individual actions to reduce exposure to pollution, provide alerts on high pollution days, and ozone and particulate forecasting for three years ($25,000 per year for 2021, 2022, and 2023)</t>
+  </si>
+  <si>
     <t>Allegheny</t>
   </si>
   <si>
-    <t>Support was provided for public outreach</t>
-  </si>
-  <si>
-    <t>Provide guidelines for individual actions to reduce exposure to pollution, provide alerts on high pollution days, and ozone and particulate forecasting for three years ($25,000 per year for 2021, 2022, and 2023)</t>
-  </si>
-  <si>
     <t>9/2/20. Ongoing</t>
   </si>
   <si>
     <t>Equipment for Air Toxics and H2S Studies</t>
   </si>
   <si>
-    <t>Operational Funding/Research</t>
+    <t>Operational Funding, Research</t>
   </si>
   <si>
     <t>ACHD</t>
   </si>
   <si>
+    <t>Air Quality monitoring testing equipment has been purchased to support</t>
+  </si>
+  <si>
+    <t>Purchase air monitoring equipment, cover sampling analysis costs, and provide lab analysis in support of the Air Quality Program conducting a study of odor and air toxics emissions and H2S in the Mon Valley</t>
+  </si>
+  <si>
     <t>Monongahela</t>
-  </si>
-  <si>
-    <t>Air Quality monitoring testing equipment has been purchased to support</t>
-  </si>
-  <si>
-    <t>Purchase air monitoring equipment, cover sampling analysis costs, and provide lab analysis in support of the Air Quality Program conducting a study of odor and air toxics emissions and H2S in the Mon Valley</t>
   </si>
   <si>
     <t>Completed 2024</t>
@@ -640,9 +628,6 @@
     <t>Mon Valley Municipalities Fleet Electrification</t>
   </si>
   <si>
-    <t>Electric Vehicles/Electrification/Diesel Reduction</t>
-  </si>
-  <si>
     <t xml:space="preserve">Steel Rivers Council of Governments </t>
   </si>
   <si>
@@ -655,15 +640,15 @@
     <t>Borough of Swissvale</t>
   </si>
   <si>
+    <t>Project is ongoing</t>
+  </si>
+  <si>
+    <t>Replace existing 2016 diesel powered garbage truck and 2014 recycling truck and purchase of an equivalent electric garbage truck and recycling truck and installation of two electric vehicle charging stations at the borough's Public Works Department</t>
+  </si>
+  <si>
     <t>Swissvale</t>
   </si>
   <si>
-    <t>Project is ongoing</t>
-  </si>
-  <si>
-    <t>Replace existing 2016 diesel powered garbage truck and 2014 recycling truck and purchase of an equivalent electric garbage truck and recycling truck and installation of two electric vehicle charging stations at the borough's Public Works Department</t>
-  </si>
-  <si>
     <t>Tree planting in Allegheny County, one per child</t>
   </si>
   <si>
@@ -679,15 +664,15 @@
     <t>West Mifflin Borough</t>
   </si>
   <si>
+    <t>The charging station has been installed and the new electric vehicle has been ordered.</t>
+  </si>
+  <si>
+    <t>Decommission and replace existing 2007 diesel-powered refuse hauler truck and replace with electric rear-load garbage packer and installation of two electric vehicle charging stations and an electrical service upgrade at the vehicle site.</t>
+  </si>
+  <si>
     <t>West Mifflin</t>
   </si>
   <si>
-    <t>The charging station has been installed and the new electric vehicle has been ordered.</t>
-  </si>
-  <si>
-    <t>Decommission and replace existing 2007 diesel-powered refuse hauler truck and replace with electric rear-load garbage packer and installation of two electric vehicle charging stations and an electrical service upgrade at the vehicle site.</t>
-  </si>
-  <si>
     <t>Ongoing through 2030</t>
   </si>
   <si>
@@ -697,15 +682,15 @@
     <t>Wilkinsburg Shade Tree Commission</t>
   </si>
   <si>
+    <t>Ongoing</t>
+  </si>
+  <si>
+    <t>Plant and maintain 50 Trees in Wilkinsburg</t>
+  </si>
+  <si>
     <t>Wilkinsburg</t>
   </si>
   <si>
-    <t>Ongoing</t>
-  </si>
-  <si>
-    <t>Plant and maintain 50 Trees in Wilkinsburg</t>
-  </si>
-  <si>
     <t>Plant and maintain 45 trees in Monongahela Valley communities</t>
   </si>
   <si>
@@ -721,33 +706,33 @@
     <t>Borough of Brackenridge</t>
   </si>
   <si>
+    <t>Replace eleven gas powered pieces of municipal lawn equipment with electric models</t>
+  </si>
+  <si>
     <t>Brackenridge</t>
   </si>
   <si>
-    <t>Replace eleven gas powered pieces of municipal lawn equipment with electric models</t>
-  </si>
-  <si>
     <t>Municipal Equipment Electrification </t>
   </si>
   <si>
     <t> Borough of Pitcairn</t>
   </si>
   <si>
+    <t>Replace 20 gas powered pieces of municipal lawn equipment with electric models</t>
+  </si>
+  <si>
     <t>Pitcairn</t>
   </si>
   <si>
-    <t>Replace 20 gas powered pieces of municipal lawn equipment with electric models</t>
-  </si>
-  <si>
     <t>The Boroughs of Braddock, North Braddock, Rankin, and East Pittsburgh</t>
   </si>
   <si>
+    <t>Replace four gas powered pieces of municipal lawn equipment with electric models for the boroughs of Braddock, East Pittsburgh, North Braddock, and Rankin</t>
+  </si>
+  <si>
     <t>Braddock, Rankin, Pittsburgh</t>
   </si>
   <si>
-    <t>Replace four gas powered pieces of municipal lawn equipment with electric models for the boroughs of Braddock, East Pittsburgh, North Braddock, and Rankin</t>
-  </si>
-  <si>
     <t>Ongoing through 2027</t>
   </si>
   <si>
@@ -760,12 +745,12 @@
     <t>Munhall Borough</t>
   </si>
   <si>
+    <t>Support the replacement of three diesel refuse trucks with electric models and charging infrastructure</t>
+  </si>
+  <si>
     <t>Munhall</t>
   </si>
   <si>
-    <t>Support the replacement of three diesel refuse trucks with electric models and charging infrastructure</t>
-  </si>
-  <si>
     <t>Climate Resilience</t>
   </si>
   <si>
@@ -778,22 +763,22 @@
     <t>Sharpsburg Borough</t>
   </si>
   <si>
+    <t>Funding to install a solar panel and battery storage system to offset the borough building's electrical usage and to provide backup power in the event of outages</t>
+  </si>
+  <si>
     <t>Sharpsburgh</t>
   </si>
   <si>
-    <t>Funding to install a solar panel and battery storage system to offset the borough building's electrical usage and to provide backup power in the event of outages</t>
-  </si>
-  <si>
     <t>Tree Planting, Emission Reduction</t>
   </si>
   <si>
     <t xml:space="preserve">Borough of Etna	</t>
   </si>
   <si>
+    <t>Funding to assist the installation of solar panels, green building technologies, and tree planting at their new municipal office building</t>
+  </si>
+  <si>
     <t>Etna</t>
-  </si>
-  <si>
-    <t>Funding to assist the installation of solar panels, green building technologies, and tree planting at their new municipal office building</t>
   </si>
   <si>
     <t>Pittsburgh International Science &amp; Technology Festival</t>
@@ -1187,12 +1172,6 @@
   </si>
   <si>
     <t>Project Category 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Education/Competition</t>
-  </si>
-  <si>
-    <t>Public Communications</t>
   </si>
   <si>
     <t>Software</t>
@@ -1205,7 +1184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1277,9 +1256,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="19">
@@ -1404,7 +1397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1520,7 +1513,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1587,9 +1579,6 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1606,9 +1595,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1712,80 +1698,51 @@
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1794,10 +1751,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFEB94"/>
       <color rgb="FF00EDEA"/>
-      <color rgb="FFFFFF82"/>
+      <color rgb="FFFFEC00"/>
       <color rgb="FFD609CF"/>
-      <color rgb="FFFFEC00"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2129,7 +2086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7BBCAD-3B48-6E4F-9C93-0877622E7CFE}">
   <dimension ref="A1:FT140"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="5" customWidth="1"/>
     <col min="2" max="2" width="11.125" style="5" customWidth="1"/>
@@ -2137,14 +2094,14 @@
     <col min="4" max="4" width="57.125" style="5" customWidth="1"/>
     <col min="5" max="5" width="42.375" style="5" customWidth="1"/>
     <col min="6" max="6" width="45.125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="20.375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="49.625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="139.125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="26.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="49.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="139.125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="26.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="5" customWidth="1"/>
     <col min="11" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="33.950000000000003">
+    <row r="1" spans="1:21" ht="17.100000000000001">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2206,11 +2163,11 @@
       <c r="F2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="25"/>
+      <c r="H2" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="65" t="s">
+      <c r="J2" s="25" t="s">
         <v>14</v>
       </c>
       <c r="K2" s="1"/>
@@ -2244,11 +2201,11 @@
       <c r="F3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="62" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="66" t="s">
+      <c r="J3" s="61" t="s">
         <v>19</v>
       </c>
       <c r="K3" s="1"/>
@@ -2263,7 +2220,7 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="1:21" ht="30.75">
+    <row r="4" spans="1:21" ht="33.950000000000003">
       <c r="A4" s="11">
         <v>2015</v>
       </c>
@@ -2277,16 +2234,16 @@
         <v>20</v>
       </c>
       <c r="E4" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="G4" s="25"/>
+      <c r="H4" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="65" t="s">
-        <v>23</v>
-      </c>
+      <c r="J4" s="25"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -2299,7 +2256,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="1:21" ht="30.75">
+    <row r="5" spans="1:21" ht="33.950000000000003">
       <c r="A5" s="11">
         <v>2015</v>
       </c>
@@ -2310,19 +2267,19 @@
         <v>337600</v>
       </c>
       <c r="D5" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="F5" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="G5" s="38"/>
+      <c r="H5" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="67" t="s">
-        <v>27</v>
-      </c>
+      <c r="J5" s="38"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2335,34 +2292,34 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" spans="1:21" ht="30.75">
+    <row r="6" spans="1:21" ht="33.950000000000003">
       <c r="A6" s="11">
         <v>2015</v>
       </c>
       <c r="B6" s="13">
         <v>42249</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="55">
         <v>400000</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="F6" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="G6" s="48"/>
+      <c r="H6" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="I6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="68" t="s">
+      <c r="J6" s="48" t="s">
         <v>32</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -2376,7 +2333,7 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="1:21" ht="30.75">
+    <row r="7" spans="1:21" ht="33.950000000000003">
       <c r="A7" s="11">
         <v>2016</v>
       </c>
@@ -2386,19 +2343,21 @@
       <c r="C7" s="14">
         <v>450000</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="F7" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="G7" s="47"/>
+      <c r="H7" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="69" t="s">
-        <v>37</v>
+      <c r="J7" s="47" t="s">
+        <v>32</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -2412,33 +2371,30 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="1:21" ht="15.75">
+    <row r="8" spans="1:21" ht="17.100000000000001">
       <c r="A8" s="11">
         <v>2016</v>
       </c>
       <c r="B8" s="13">
         <v>42382</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="55">
         <v>78000</v>
       </c>
       <c r="D8" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="87" t="s">
+      <c r="G8" s="25"/>
+      <c r="H8" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>42</v>
-      </c>
+      <c r="J8" s="25"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2451,7 +2407,7 @@
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
     </row>
-    <row r="9" spans="1:21" ht="30.75">
+    <row r="9" spans="1:21" ht="33.950000000000003">
       <c r="A9" s="11">
         <v>2016</v>
       </c>
@@ -2461,21 +2417,21 @@
       <c r="C9" s="14">
         <v>717246</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="51"/>
+      <c r="H9" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="J9" s="51" t="s">
         <v>44</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="52"/>
-      <c r="I9" s="70" t="s">
-        <v>47</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2489,7 +2445,7 @@
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
     </row>
-    <row r="10" spans="1:21" ht="30.75">
+    <row r="10" spans="1:21" ht="33.950000000000003">
       <c r="A10" s="11">
         <v>2016</v>
       </c>
@@ -2499,21 +2455,21 @@
       <c r="C10" s="14">
         <v>180000</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="48"/>
+      <c r="H10" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="49"/>
-      <c r="I10" s="68" t="s">
-        <v>51</v>
+      <c r="J10" s="48" t="s">
+        <v>32</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -2527,7 +2483,7 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" spans="1:21" ht="30.75">
+    <row r="11" spans="1:21" ht="33.950000000000003">
       <c r="A11" s="11">
         <v>2016</v>
       </c>
@@ -2537,20 +2493,20 @@
       <c r="C11" s="24">
         <v>50000</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="68" t="s">
-        <v>55</v>
-      </c>
+      <c r="D11" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="48"/>
+      <c r="H11" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="48"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2563,33 +2519,30 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" spans="1:21" ht="30.75">
+    <row r="12" spans="1:21" ht="33.950000000000003">
       <c r="A12" s="11">
         <v>2016</v>
       </c>
       <c r="B12" s="13">
         <v>42494</v>
       </c>
-      <c r="C12" s="106">
+      <c r="C12" s="103">
         <v>24000</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="D12" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="112"/>
+      <c r="H12" s="113" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="109"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2602,7 +2555,7 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
     </row>
-    <row r="13" spans="1:21" ht="15.75">
+    <row r="13" spans="1:21" ht="17.100000000000001">
       <c r="A13" s="11">
         <v>2016</v>
       </c>
@@ -2613,20 +2566,20 @@
         <v>4000</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>57</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="65" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>60</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -2640,7 +2593,7 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
     </row>
-    <row r="14" spans="1:21" ht="30.75">
+    <row r="14" spans="1:21" ht="33.950000000000003">
       <c r="A14" s="11">
         <v>2016</v>
       </c>
@@ -2650,23 +2603,20 @@
       <c r="C14" s="24">
         <v>75900</v>
       </c>
-      <c r="D14" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="88" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="D14" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="85"/>
+      <c r="H14" s="107" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="85"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2679,7 +2629,7 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
     </row>
-    <row r="15" spans="1:21" ht="15.75">
+    <row r="15" spans="1:21" ht="17.100000000000001">
       <c r="A15" s="11">
         <v>2017</v>
       </c>
@@ -2690,20 +2640,20 @@
         <v>7500</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="65" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="G15" s="25"/>
+      <c r="H15" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>60</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -2717,33 +2667,33 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
     </row>
-    <row r="16" spans="1:21" ht="30.75">
+    <row r="16" spans="1:21" ht="33.950000000000003">
       <c r="A16" s="11">
         <v>2017</v>
       </c>
       <c r="B16" s="13">
         <v>42746</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="55">
         <v>65000</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="89" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="89" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="65" t="s">
-        <v>75</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="86"/>
+      <c r="H16" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="25"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2756,7 +2706,7 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" spans="1:21" ht="30.75">
+    <row r="17" spans="1:21" ht="33.950000000000003">
       <c r="A17" s="11">
         <v>2018</v>
       </c>
@@ -2766,19 +2716,21 @@
       <c r="C17" s="14">
         <v>45000</v>
       </c>
-      <c r="D17" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="72" t="s">
-        <v>78</v>
+      <c r="D17" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="62"/>
+      <c r="H17" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -2792,7 +2744,7 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" spans="1:21" ht="15.75">
+    <row r="18" spans="1:21" ht="33.950000000000003">
       <c r="A18" s="11">
         <v>2018</v>
       </c>
@@ -2802,21 +2754,21 @@
       <c r="C18" s="14">
         <v>300000</v>
       </c>
-      <c r="D18" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="49"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="D18" s="108" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="48"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="85"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2829,7 +2781,7 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" spans="1:21" ht="15.75">
+    <row r="19" spans="1:21" ht="33.950000000000003">
       <c r="A19" s="11">
         <v>2018</v>
       </c>
@@ -2839,19 +2791,21 @@
       <c r="C19" s="14">
         <v>558242</v>
       </c>
-      <c r="D19" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="63" t="s">
+      <c r="D19" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="72" t="s">
-        <v>82</v>
+      <c r="G19" s="62"/>
+      <c r="H19" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -2865,7 +2819,7 @@
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
     </row>
-    <row r="20" spans="1:21" ht="30.75">
+    <row r="20" spans="1:21" ht="33.950000000000003">
       <c r="A20" s="11">
         <v>2018</v>
       </c>
@@ -2875,19 +2829,21 @@
       <c r="C20" s="14">
         <v>66000</v>
       </c>
-      <c r="D20" s="69" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="69" t="s">
-        <v>83</v>
+      <c r="D20" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="47"/>
+      <c r="H20" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -2901,7 +2857,7 @@
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" spans="1:21" ht="15.75">
+    <row r="21" spans="1:21" ht="33.950000000000003">
       <c r="A21" s="11">
         <v>2018</v>
       </c>
@@ -2911,19 +2867,21 @@
       <c r="C21" s="14">
         <v>579703</v>
       </c>
-      <c r="D21" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="47" t="s">
+      <c r="D21" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="69" t="s">
-        <v>85</v>
+      <c r="G21" s="47"/>
+      <c r="H21" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -2937,7 +2895,7 @@
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" spans="1:21" ht="15.75">
+    <row r="22" spans="1:21" ht="33.950000000000003">
       <c r="A22" s="11">
         <v>2018</v>
       </c>
@@ -2947,19 +2905,21 @@
       <c r="C22" s="14">
         <v>546017</v>
       </c>
-      <c r="D22" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="48" t="s">
+      <c r="D22" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="69" t="s">
-        <v>86</v>
+      <c r="G22" s="47"/>
+      <c r="H22" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -2973,7 +2933,7 @@
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" spans="1:21" ht="30.75">
+    <row r="23" spans="1:21" ht="33.950000000000003">
       <c r="A23" s="11">
         <v>2018</v>
       </c>
@@ -2983,19 +2943,21 @@
       <c r="C23" s="14">
         <v>60000</v>
       </c>
-      <c r="D23" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="69" t="s">
-        <v>87</v>
+      <c r="D23" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="47"/>
+      <c r="H23" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -3009,7 +2971,7 @@
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" spans="1:21" ht="15.75">
+    <row r="24" spans="1:21" ht="33.950000000000003">
       <c r="A24" s="11">
         <v>2019</v>
       </c>
@@ -3019,19 +2981,21 @@
       <c r="C24" s="14">
         <v>24765</v>
       </c>
-      <c r="D24" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="69" t="s">
-        <v>89</v>
+      <c r="D24" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="47"/>
+      <c r="H24" s="67" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -3045,7 +3009,7 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="1:21" ht="30.75">
+    <row r="25" spans="1:21" ht="33.950000000000003">
       <c r="A25" s="11">
         <v>2019</v>
       </c>
@@ -3055,22 +3019,24 @@
       <c r="C25" s="14">
         <v>15000</v>
       </c>
-      <c r="D25" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="69" t="s">
-        <v>91</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>33</v>
+      <c r="D25" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="85" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="47"/>
+      <c r="H25" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="108" t="s">
+        <v>32</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -3084,7 +3050,7 @@
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" spans="1:21" ht="46.5">
+    <row r="26" spans="1:21" ht="51">
       <c r="A26" s="11">
         <v>2019</v>
       </c>
@@ -3094,21 +3060,23 @@
       <c r="C26" s="14">
         <v>120000</v>
       </c>
-      <c r="D26" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="53" t="s">
+      <c r="D26" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="J26" s="11"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="11"/>
+      <c r="J26" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -3121,7 +3089,7 @@
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="1:21" ht="15.75">
+    <row r="27" spans="1:21" ht="17.100000000000001">
       <c r="A27" s="11">
         <v>2019</v>
       </c>
@@ -3131,21 +3099,21 @@
       <c r="C27" s="14">
         <v>150000</v>
       </c>
-      <c r="D27" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="55" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" s="11"/>
+      <c r="D27" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="54"/>
+      <c r="H27" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -3158,7 +3126,7 @@
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
     </row>
-    <row r="28" spans="1:21" ht="30.75">
+    <row r="28" spans="1:21" ht="33.950000000000003">
       <c r="A28" s="11">
         <v>2019</v>
       </c>
@@ -3169,22 +3137,22 @@
         <v>300000</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="54"/>
-      <c r="I28" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="J28" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="53"/>
+      <c r="H28" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" s="11"/>
+      <c r="J28" s="53" t="s">
+        <v>32</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -3197,7 +3165,7 @@
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
     </row>
-    <row r="29" spans="1:21" ht="30.75">
+    <row r="29" spans="1:21" ht="33.950000000000003">
       <c r="A29" s="11">
         <v>2019</v>
       </c>
@@ -3214,14 +3182,14 @@
         <v>16</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="76" t="s">
-        <v>100</v>
-      </c>
-      <c r="J29" s="11"/>
+      <c r="H29" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="11"/>
+      <c r="J29" s="18"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -3234,7 +3202,7 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="1:21" ht="30.75">
+    <row r="30" spans="1:21" ht="33.950000000000003">
       <c r="A30" s="11">
         <v>2019</v>
       </c>
@@ -3244,21 +3212,21 @@
       <c r="C30" s="14">
         <v>627100</v>
       </c>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="G30" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="H30" s="55"/>
-      <c r="I30" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="J30" s="11"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="54"/>
+      <c r="H30" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I30" s="11"/>
+      <c r="J30" s="54" t="s">
+        <v>99</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -3271,31 +3239,28 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="1:21" ht="30.75">
+    <row r="31" spans="1:21" ht="33.950000000000003">
       <c r="A31" s="11">
         <v>2020</v>
       </c>
       <c r="B31" s="13">
         <v>43840</v>
       </c>
-      <c r="C31" s="56">
+      <c r="C31" s="55">
         <v>25000</v>
       </c>
-      <c r="D31" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="D31" s="110" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="109"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="110" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="109"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -3308,7 +3273,7 @@
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
     </row>
-    <row r="32" spans="1:21" ht="30.75">
+    <row r="32" spans="1:21" ht="33.950000000000003">
       <c r="A32" s="11">
         <v>2020</v>
       </c>
@@ -3318,23 +3283,23 @@
       <c r="C32" s="14">
         <v>9000</v>
       </c>
-      <c r="D32" s="77" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="77" t="s">
-        <v>105</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>107</v>
-      </c>
+      <c r="D32" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="43"/>
+      <c r="H32" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" s="43"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -3347,7 +3312,7 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
     </row>
-    <row r="33" spans="1:21" ht="30.75">
+    <row r="33" spans="1:21" ht="33.950000000000003">
       <c r="A33" s="11">
         <v>2020</v>
       </c>
@@ -3357,23 +3322,23 @@
       <c r="C33" s="14">
         <v>7500</v>
       </c>
-      <c r="D33" s="77" t="s">
-        <v>108</v>
+      <c r="D33" s="74" t="s">
+        <v>104</v>
       </c>
       <c r="E33" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F33" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="77" t="s">
-        <v>108</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>110</v>
-      </c>
+      <c r="F33" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="43"/>
+      <c r="H33" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J33" s="43"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -3386,7 +3351,7 @@
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
     </row>
-    <row r="34" spans="1:21" ht="15.75">
+    <row r="34" spans="1:21" ht="33.950000000000003">
       <c r="A34" s="11">
         <v>2020</v>
       </c>
@@ -3396,21 +3361,23 @@
       <c r="C34" s="14">
         <v>592822</v>
       </c>
-      <c r="D34" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="E34" s="47" t="s">
+      <c r="D34" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F34" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="J34" s="11"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="11"/>
+      <c r="J34" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -3423,7 +3390,7 @@
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="1:21" ht="46.5">
+    <row r="35" spans="1:21" ht="51">
       <c r="A35" s="11">
         <v>2020</v>
       </c>
@@ -3433,21 +3400,23 @@
       <c r="C35" s="14">
         <v>384000</v>
       </c>
-      <c r="D35" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="J35" s="6"/>
+      <c r="D35" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="52"/>
+      <c r="H35" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="I35" s="6"/>
+      <c r="J35" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -3460,7 +3429,7 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="1:21" ht="46.5">
+    <row r="36" spans="1:21" ht="51">
       <c r="A36" s="11">
         <v>2020</v>
       </c>
@@ -3470,21 +3439,23 @@
       <c r="C36" s="2">
         <v>500000</v>
       </c>
-      <c r="D36" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="47" t="s">
+      <c r="D36" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F36" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="J36" s="11"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -3497,32 +3468,34 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
     </row>
-    <row r="37" spans="1:21" ht="30.75">
+    <row r="37" spans="1:21" ht="33.950000000000003">
       <c r="A37" s="11">
         <v>2020</v>
       </c>
       <c r="B37" s="13">
         <v>44076</v>
       </c>
-      <c r="C37" s="56">
+      <c r="C37" s="55">
         <v>210000</v>
       </c>
-      <c r="D37" s="73" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="90" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="91" t="s">
-        <v>36</v>
-      </c>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="96" t="s">
-        <v>113</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>33</v>
+      <c r="D37" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="52"/>
+      <c r="H37" s="93" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -3536,7 +3509,7 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
     </row>
-    <row r="38" spans="1:21" ht="15.75">
+    <row r="38" spans="1:21" ht="17.100000000000001">
       <c r="A38" s="11">
         <v>2020</v>
       </c>
@@ -3547,20 +3520,20 @@
         <v>59560</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="76" t="s">
-        <v>116</v>
-      </c>
-      <c r="J38" s="11"/>
+      <c r="H38" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="I38" s="11"/>
+      <c r="J38" s="18"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -3573,7 +3546,7 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" spans="1:21" ht="15.75">
+    <row r="39" spans="1:21" ht="17.100000000000001">
       <c r="A39" s="11">
         <v>2020</v>
       </c>
@@ -3584,20 +3557,20 @@
         <v>98000</v>
       </c>
       <c r="D39" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>117</v>
-      </c>
       <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="76" t="s">
-        <v>118</v>
-      </c>
-      <c r="J39" s="11"/>
+      <c r="H39" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="18"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -3610,7 +3583,7 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
     </row>
-    <row r="40" spans="1:21" ht="15.75">
+    <row r="40" spans="1:21" ht="17.100000000000001">
       <c r="A40" s="11">
         <v>2021</v>
       </c>
@@ -3620,19 +3593,21 @@
       <c r="C40" s="14">
         <v>578684</v>
       </c>
-      <c r="D40" s="53"/>
-      <c r="E40" s="47" t="s">
+      <c r="D40" s="52"/>
+      <c r="E40" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
-      <c r="I40" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="J40" s="11"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="I40" s="11"/>
+      <c r="J40" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -3645,7 +3620,7 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
     </row>
-    <row r="41" spans="1:21" ht="30.75">
+    <row r="41" spans="1:21" ht="33.950000000000003" customHeight="1">
       <c r="A41" s="11">
         <v>2021</v>
       </c>
@@ -3655,20 +3630,19 @@
       <c r="C41" s="14">
         <v>200000</v>
       </c>
-      <c r="D41" s="48"/>
-      <c r="E41" s="92" t="s">
-        <v>120</v>
-      </c>
-      <c r="F41" s="92" t="s">
-        <v>121</v>
-      </c>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="73" t="s">
-        <v>122</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>33</v>
+      <c r="D41" s="85"/>
+      <c r="E41" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="F41" s="89" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="89"/>
+      <c r="H41" s="111" t="s">
+        <v>118</v>
+      </c>
+      <c r="J41" s="108" t="s">
+        <v>32</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -3682,7 +3656,7 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
     </row>
-    <row r="42" spans="1:21" ht="30.75">
+    <row r="42" spans="1:21" ht="33.950000000000003">
       <c r="A42" s="11">
         <v>2022</v>
       </c>
@@ -3692,21 +3666,21 @@
       <c r="C42" s="14">
         <v>30000</v>
       </c>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="G42" s="84" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" s="84"/>
-      <c r="I42" s="85" t="s">
-        <v>124</v>
-      </c>
-      <c r="J42" s="11"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="81"/>
+      <c r="H42" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42" s="11"/>
+      <c r="J42" s="81" t="s">
+        <v>32</v>
+      </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -3719,7 +3693,7 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
     </row>
-    <row r="43" spans="1:21" ht="15.75">
+    <row r="43" spans="1:21" ht="17.100000000000001">
       <c r="A43" s="11">
         <v>2022</v>
       </c>
@@ -3729,19 +3703,21 @@
       <c r="C43" s="14">
         <v>539125</v>
       </c>
-      <c r="D43" s="53"/>
-      <c r="E43" s="47" t="s">
+      <c r="D43" s="52"/>
+      <c r="E43" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F43" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" s="53"/>
-      <c r="H43" s="53"/>
-      <c r="I43" s="73" t="s">
-        <v>125</v>
-      </c>
-      <c r="J43" s="11"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="11"/>
+      <c r="J43" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -3754,36 +3730,36 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
     </row>
-    <row r="44" spans="1:21" ht="61.5">
+    <row r="44" spans="1:21" ht="68.099999999999994">
       <c r="A44" s="6">
         <v>2020</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C44" s="2">
         <v>99995</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="I44" s="79" t="s">
-        <v>130</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>33</v>
+        <v>125</v>
+      </c>
+      <c r="H44" s="76" t="s">
+        <v>126</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -3797,33 +3773,33 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
     </row>
-    <row r="45" spans="1:21" ht="30.75">
+    <row r="45" spans="1:21" ht="33.950000000000003">
       <c r="A45" s="6">
         <v>2020</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C45" s="2">
         <v>15000</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="I45" s="80" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="H45" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -3837,33 +3813,33 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
     </row>
-    <row r="46" spans="1:21" ht="30.75">
+    <row r="46" spans="1:21" ht="33.950000000000003">
       <c r="A46" s="6">
         <v>2020</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C46" s="2">
         <v>98000</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="I46" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="J46" s="6"/>
+        <v>131</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="H46" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="6"/>
+      <c r="J46" s="19"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -3876,33 +3852,35 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
     </row>
-    <row r="47" spans="1:21" ht="30.75">
+    <row r="47" spans="1:21" ht="33.950000000000003">
       <c r="A47" s="6">
         <v>2020</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C47" s="2">
         <v>500000</v>
       </c>
-      <c r="D47" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="E47" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="I47" s="78" t="s">
-        <v>142</v>
-      </c>
-      <c r="J47" s="6"/>
+      <c r="D47" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="H47" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="I47" s="6"/>
+      <c r="J47" s="62" t="s">
+        <v>32</v>
+      </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -3915,34 +3893,33 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
     </row>
-    <row r="48" spans="1:21" ht="46.5">
+    <row r="48" spans="1:21" ht="51">
       <c r="A48" s="6">
         <v>2020</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C48" s="7">
         <v>55000</v>
       </c>
-      <c r="D48" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="E48" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="47" t="s">
+      <c r="D48" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="I48" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>42</v>
+      <c r="E48" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G48" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="H48" s="75" t="s">
+        <v>142</v>
+      </c>
+      <c r="J48" s="62" t="s">
+        <v>32</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -3956,36 +3933,36 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="1:43" s="86" customFormat="1" ht="46.5">
+    <row r="49" spans="1:43" s="83" customFormat="1" ht="51">
       <c r="A49" s="6">
         <v>2020</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C49" s="2">
         <v>75000</v>
       </c>
-      <c r="D49" s="47" t="s">
+      <c r="D49" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" s="91" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="H49" s="75" t="s">
+        <v>147</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="52" t="s">
         <v>148</v>
-      </c>
-      <c r="E49" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="F49" s="94" t="s">
-        <v>149</v>
-      </c>
-      <c r="G49" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="H49" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="I49" s="78" t="s">
-        <v>152</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -4021,36 +3998,36 @@
       <c r="AP49" s="5"/>
       <c r="AQ49" s="5"/>
     </row>
-    <row r="50" spans="1:43" ht="30.75">
+    <row r="50" spans="1:43" ht="33.950000000000003">
       <c r="A50" s="6">
         <v>2020</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C50" s="2">
         <v>340554</v>
       </c>
-      <c r="D50" s="47" t="s">
+      <c r="D50" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="75" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="46" t="s">
+      <c r="I50" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="46" t="s">
         <v>155</v>
-      </c>
-      <c r="F50" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="G50" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="H50" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="I50" s="78" t="s">
-        <v>159</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -4064,35 +4041,35 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="1:43" ht="30.75">
+    <row r="51" spans="1:43" ht="33.950000000000003">
       <c r="A51" s="6">
         <v>2020</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C51" s="2">
         <v>548725</v>
       </c>
-      <c r="D51" s="90" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" s="90" t="s">
-        <v>77</v>
-      </c>
-      <c r="F51" s="90" t="s">
-        <v>162</v>
-      </c>
-      <c r="G51" s="90"/>
-      <c r="H51" s="90" t="s">
-        <v>163</v>
-      </c>
-      <c r="I51" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="D51" s="87" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" s="114" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" s="114" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" s="87" t="s">
+        <v>159</v>
+      </c>
+      <c r="H51" s="92" t="s">
+        <v>160</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="87"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -4105,68 +4082,68 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="1:43" ht="30.75">
+    <row r="52" spans="1:43" ht="33.950000000000003">
       <c r="A52" s="6">
         <v>2021</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C52" s="7">
         <v>200000</v>
       </c>
-      <c r="D52" s="93" t="s">
+      <c r="D52" s="90" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="90" t="s">
+        <v>162</v>
+      </c>
+      <c r="F52" s="94" t="s">
+        <v>163</v>
+      </c>
+      <c r="G52" s="95" t="s">
+        <v>164</v>
+      </c>
+      <c r="H52" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="E52" s="93" t="s">
+      <c r="I52" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F52" s="97" t="s">
-        <v>167</v>
-      </c>
-      <c r="G52" s="93"/>
-      <c r="H52" s="98" t="s">
-        <v>168</v>
-      </c>
-      <c r="I52" s="99" t="s">
-        <v>169</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>170</v>
-      </c>
+      <c r="J52" s="90"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
     </row>
-    <row r="53" spans="1:43" s="25" customFormat="1" ht="30.75">
+    <row r="53" spans="1:43" s="25" customFormat="1" ht="33.950000000000003">
       <c r="A53" s="6">
         <v>2021</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C53" s="4">
         <v>9941</v>
       </c>
-      <c r="D53" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F53" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="G53" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="H53" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="I53" s="81" t="s">
-        <v>175</v>
-      </c>
-      <c r="J53" s="6"/>
+      <c r="D53" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="G53" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="H53" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="I53" s="6"/>
+      <c r="J53" s="45" t="s">
+        <v>155</v>
+      </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -4201,141 +4178,135 @@
       <c r="AP53" s="5"/>
       <c r="AQ53" s="5"/>
     </row>
-    <row r="54" spans="1:43" ht="30.75">
+    <row r="54" spans="1:43" ht="35.1">
       <c r="A54" s="6">
         <v>2021</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C54" s="4">
         <v>69956</v>
       </c>
-      <c r="D54" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F54" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="G54" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="H54" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="I54" s="81" t="s">
-        <v>179</v>
-      </c>
-      <c r="J54" s="6"/>
+      <c r="D54" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="G54" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="H54" s="78" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" s="6"/>
+      <c r="J54" s="45" t="s">
+        <v>155</v>
+      </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
     </row>
-    <row r="55" spans="1:43" ht="46.5">
+    <row r="55" spans="1:43" ht="51">
       <c r="A55" s="6">
         <v>2023</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C55" s="2">
         <v>9000</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E55" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="I55" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="J55" s="6"/>
-    </row>
-    <row r="56" spans="1:43" ht="61.5">
+        <v>177</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="H55" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="I55" s="6"/>
+      <c r="J55" s="20"/>
+    </row>
+    <row r="56" spans="1:43" ht="68.099999999999994">
       <c r="A56" s="6">
         <v>2023</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C56" s="2">
         <v>750000</v>
       </c>
-      <c r="D56" s="101" t="s">
-        <v>185</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F56" s="101" t="s">
-        <v>187</v>
-      </c>
-      <c r="G56" s="101"/>
-      <c r="H56" s="101" t="s">
-        <v>188</v>
-      </c>
-      <c r="I56" s="102" t="s">
-        <v>189</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:43" ht="61.5">
+      <c r="D56" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="98" t="s">
+        <v>182</v>
+      </c>
+      <c r="G56" s="98" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="J56" s="98"/>
+    </row>
+    <row r="57" spans="1:43" ht="68.099999999999994">
       <c r="A57" s="6">
         <v>2023</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C57" s="2">
         <v>700000</v>
       </c>
-      <c r="D57" s="101" t="s">
+      <c r="D57" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="E57" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="E57" s="39" t="s">
+      <c r="G57" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="F57" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="G57" s="101" t="s">
-        <v>191</v>
-      </c>
-      <c r="H57" s="101" t="s">
-        <v>192</v>
-      </c>
-      <c r="I57" s="102" t="s">
-        <v>193</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:43" ht="61.5">
+      <c r="H57" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="J57" s="98" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:43" ht="68.099999999999994">
       <c r="A58" s="6">
         <v>2023</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C58" s="2">
         <v>46000</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>16</v>
@@ -4344,28 +4315,28 @@
         <v>17</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="I58" s="79" t="s">
-        <v>195</v>
-      </c>
-      <c r="J58" s="6"/>
-    </row>
-    <row r="59" spans="1:43" ht="61.5">
+        <v>186</v>
+      </c>
+      <c r="H58" s="76" t="s">
+        <v>190</v>
+      </c>
+      <c r="I58" s="6"/>
+      <c r="J58" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:43" ht="68.099999999999994">
       <c r="A59" s="6">
         <v>2023</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C59" s="2">
         <v>46000</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>16</v>
@@ -4374,363 +4345,345 @@
         <v>17</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="I59" s="79" t="s">
-        <v>196</v>
-      </c>
-      <c r="J59" s="6"/>
-    </row>
-    <row r="60" spans="1:43" ht="61.5">
+        <v>186</v>
+      </c>
+      <c r="H59" s="76" t="s">
+        <v>191</v>
+      </c>
+      <c r="I59" s="6"/>
+      <c r="J59" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:43" ht="68.099999999999994">
       <c r="A60" s="6">
         <v>2023</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C60" s="2">
         <v>748339</v>
       </c>
-      <c r="D60" s="103" t="s">
-        <v>197</v>
-      </c>
-      <c r="E60" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F60" s="101" t="s">
-        <v>198</v>
-      </c>
-      <c r="G60" s="101" t="s">
-        <v>199</v>
-      </c>
-      <c r="H60" s="101" t="s">
-        <v>200</v>
-      </c>
-      <c r="I60" s="102" t="s">
-        <v>201</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:43" ht="46.5">
+      <c r="D60" s="100" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F60" s="98" t="s">
+        <v>193</v>
+      </c>
+      <c r="G60" s="98" t="s">
+        <v>194</v>
+      </c>
+      <c r="H60" s="99" t="s">
+        <v>195</v>
+      </c>
+      <c r="J60" s="98" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:43" ht="51">
       <c r="A61" s="6">
         <v>2024</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C61" s="2">
         <v>46000</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="G61" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="I61" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="J61" s="6"/>
-    </row>
-    <row r="62" spans="1:43" ht="46.5">
+        <v>199</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="I61" s="6"/>
+      <c r="J61" s="40" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" spans="1:43" ht="51">
       <c r="A62" s="6">
         <v>2024</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C62" s="2">
         <v>46000</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="G62" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="I62" s="79" t="s">
-        <v>208</v>
-      </c>
-      <c r="J62" s="6"/>
-    </row>
-    <row r="63" spans="1:43" ht="46.5">
+        <v>131</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H62" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="I62" s="6"/>
+      <c r="J62" s="40" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:43" ht="51">
       <c r="A63" s="6">
         <v>2024</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" s="98" t="s">
+        <v>206</v>
+      </c>
+      <c r="E63" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F63" s="98" t="s">
+        <v>207</v>
+      </c>
+      <c r="G63" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="H63" s="99" t="s">
+        <v>208</v>
+      </c>
+      <c r="J63" s="98" t="s">
         <v>209</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D63" s="101" t="s">
-        <v>211</v>
-      </c>
-      <c r="E63" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F63" s="101" t="s">
-        <v>212</v>
-      </c>
-      <c r="G63" s="101" t="s">
-        <v>213</v>
-      </c>
-      <c r="H63" s="101" t="s">
-        <v>206</v>
-      </c>
-      <c r="I63" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64" spans="1:43" ht="46.5">
+    </row>
+    <row r="64" spans="1:43" ht="51">
       <c r="A64" s="6">
         <v>2024</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C64" s="2">
         <v>43272</v>
       </c>
-      <c r="D64" s="101" t="s">
-        <v>215</v>
-      </c>
-      <c r="E64" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F64" s="101" t="s">
-        <v>216</v>
-      </c>
-      <c r="G64" s="104" t="s">
-        <v>217</v>
-      </c>
-      <c r="H64" s="101" t="s">
-        <v>206</v>
-      </c>
-      <c r="I64" s="102" t="s">
-        <v>218</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="46.5">
+      <c r="D64" s="98" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F64" s="98" t="s">
+        <v>211</v>
+      </c>
+      <c r="G64" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="H64" s="99" t="s">
+        <v>212</v>
+      </c>
+      <c r="J64" s="101" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="51">
       <c r="A65" s="6">
         <v>2024</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C65" s="2">
         <v>75000</v>
       </c>
-      <c r="D65" s="101" t="s">
-        <v>211</v>
-      </c>
-      <c r="E65" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F65" s="101" t="s">
-        <v>219</v>
-      </c>
-      <c r="G65" s="104" t="s">
-        <v>220</v>
-      </c>
-      <c r="H65" s="101" t="s">
+      <c r="D65" s="98" t="s">
         <v>206</v>
       </c>
-      <c r="I65" s="102" t="s">
-        <v>221</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="46.5">
+      <c r="E65" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F65" s="98" t="s">
+        <v>214</v>
+      </c>
+      <c r="G65" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="H65" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="J65" s="101" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="51">
       <c r="A66" s="6">
         <v>2024</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C66" s="2">
         <v>800000</v>
       </c>
-      <c r="D66" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="E66" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F66" s="101" t="s">
-        <v>190</v>
-      </c>
-      <c r="G66" s="104" t="s">
-        <v>191</v>
-      </c>
-      <c r="H66" s="101" t="s">
-        <v>206</v>
-      </c>
-      <c r="I66" s="102" t="s">
-        <v>224</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="46.5">
+      <c r="D66" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="E66" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F66" s="98" t="s">
+        <v>185</v>
+      </c>
+      <c r="G66" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="H66" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="J66" s="101" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="51">
       <c r="A67" s="6">
         <v>2024</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C67" s="2">
         <v>186789</v>
       </c>
-      <c r="D67" s="101" t="s">
-        <v>223</v>
-      </c>
-      <c r="E67" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="F67" s="101" t="s">
-        <v>225</v>
-      </c>
-      <c r="G67" s="104" t="s">
-        <v>226</v>
-      </c>
-      <c r="H67" s="101" t="s">
-        <v>206</v>
-      </c>
-      <c r="I67" s="102" t="s">
-        <v>227</v>
-      </c>
-      <c r="J67" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="46.5">
+      <c r="D67" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="E67" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="F67" s="98" t="s">
+        <v>220</v>
+      </c>
+      <c r="G67" s="98" t="s">
+        <v>200</v>
+      </c>
+      <c r="H67" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="J67" s="101" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="51">
       <c r="A68" s="6">
         <v>2024</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C68" s="2">
         <v>997450</v>
       </c>
-      <c r="D68" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="E68" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="F68" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="G68" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="H68" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="I68" s="82" t="s">
-        <v>229</v>
-      </c>
-      <c r="J68" s="6"/>
-    </row>
-    <row r="69" spans="1:10" ht="46.5">
+      <c r="D68" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="E68" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="G68" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="H68" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="I68" s="6"/>
+      <c r="J68" s="50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="51">
       <c r="A69" s="6">
         <v>2024</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C69" s="2">
         <v>1000000</v>
       </c>
-      <c r="D69" s="50" t="s">
-        <v>230</v>
-      </c>
-      <c r="E69" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="F69" s="50" t="s">
-        <v>231</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="H69" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="I69" s="82" t="s">
-        <v>233</v>
-      </c>
-      <c r="J69" s="6"/>
-    </row>
-    <row r="70" spans="1:10" ht="46.5">
+      <c r="D69" s="49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E69" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="F69" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="G69" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="H69" s="79" t="s">
+        <v>227</v>
+      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="51">
       <c r="A70" s="6">
         <v>2024</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C70" s="2">
         <v>500000</v>
       </c>
-      <c r="D70" s="50" t="s">
+      <c r="D70" s="49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="F70" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="G70" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="H70" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="I70" s="82" t="s">
-        <v>237</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>33</v>
+      <c r="G70" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="H70" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="50" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1">
-      <c r="G71" s="105"/>
-      <c r="H71" s="105"/>
+      <c r="G71" s="102"/>
+      <c r="J71" s="102"/>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1"/>
     <row r="73" spans="1:10" ht="15" customHeight="1"/>
@@ -4747,8 +4700,21 @@
     <row r="84" ht="15" customHeight="1"/>
     <row r="85" ht="15" customHeight="1"/>
     <row r="86" ht="15" customHeight="1"/>
+    <row r="87" ht="15.95"/>
+    <row r="88" ht="15.95"/>
+    <row r="89" ht="15.95"/>
+    <row r="90" ht="15.95"/>
+    <row r="91" ht="15.95"/>
+    <row r="92" ht="15.95"/>
+    <row r="93" ht="15.95"/>
+    <row r="94" ht="15.95"/>
     <row r="95" ht="17.100000000000001" customHeight="1"/>
-    <row r="101" spans="1:176" s="45" customFormat="1">
+    <row r="96" ht="15.95"/>
+    <row r="97" spans="1:176" ht="15.95"/>
+    <row r="98" spans="1:176" ht="15.95"/>
+    <row r="99" spans="1:176" ht="15.95"/>
+    <row r="100" spans="1:176" ht="15.95"/>
+    <row r="101" spans="1:176" s="44" customFormat="1" ht="15.95">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -4926,7 +4892,9 @@
       <c r="FS101" s="5"/>
       <c r="FT101" s="5"/>
     </row>
-    <row r="104" spans="1:176" s="45" customFormat="1">
+    <row r="102" spans="1:176" ht="15.95"/>
+    <row r="103" spans="1:176" ht="15.95"/>
+    <row r="104" spans="1:176" s="44" customFormat="1" ht="15.95">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -5104,7 +5072,7 @@
       <c r="FS104" s="5"/>
       <c r="FT104" s="5"/>
     </row>
-    <row r="105" spans="1:176" s="45" customFormat="1">
+    <row r="105" spans="1:176" s="44" customFormat="1" ht="15.95">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -5282,7 +5250,7 @@
       <c r="FS105" s="5"/>
       <c r="FT105" s="5"/>
     </row>
-    <row r="106" spans="1:176" s="25" customFormat="1">
+    <row r="106" spans="1:176" s="25" customFormat="1" ht="15.95">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -5460,7 +5428,7 @@
       <c r="FS106" s="5"/>
       <c r="FT106" s="5"/>
     </row>
-    <row r="107" spans="1:176" s="45" customFormat="1">
+    <row r="107" spans="1:176" s="44" customFormat="1" ht="15.95">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -5638,7 +5606,10 @@
       <c r="FS107" s="5"/>
       <c r="FT107" s="5"/>
     </row>
-    <row r="111" spans="1:176" s="48" customFormat="1">
+    <row r="108" spans="1:176" ht="15.95"/>
+    <row r="109" spans="1:176" ht="15.95"/>
+    <row r="110" spans="1:176" ht="15.95"/>
+    <row r="111" spans="1:176" s="47" customFormat="1" ht="15.95">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -5816,7 +5787,10 @@
       <c r="FS111" s="5"/>
       <c r="FT111" s="5"/>
     </row>
-    <row r="115" spans="1:176" s="48" customFormat="1">
+    <row r="112" spans="1:176" ht="15.95"/>
+    <row r="113" spans="1:176" ht="15.95"/>
+    <row r="114" spans="1:176" ht="15.95"/>
+    <row r="115" spans="1:176" s="47" customFormat="1" ht="15.95">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -5994,7 +5968,26 @@
       <c r="FS115" s="5"/>
       <c r="FT115" s="5"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="116" spans="1:176" ht="15.95"/>
+    <row r="117" spans="1:176" ht="15.95"/>
+    <row r="118" spans="1:176" ht="15.95"/>
+    <row r="119" spans="1:176" ht="15.95"/>
+    <row r="120" spans="1:176" ht="15.95"/>
+    <row r="121" spans="1:176" ht="15.95"/>
+    <row r="122" spans="1:176" ht="15.95"/>
+    <row r="123" spans="1:176" ht="15.95"/>
+    <row r="124" spans="1:176" ht="15.95"/>
+    <row r="125" spans="1:176" ht="15.95"/>
+    <row r="126" spans="1:176" ht="15.95"/>
+    <row r="127" spans="1:176" ht="15.95"/>
+    <row r="128" spans="1:176" ht="15.95"/>
+    <row r="129" spans="1:10" ht="15.95"/>
+    <row r="130" spans="1:10" ht="15.95"/>
+    <row r="131" spans="1:10" ht="15.95"/>
+    <row r="132" spans="1:10" ht="15.95"/>
+    <row r="133" spans="1:10" ht="15.95"/>
+    <row r="134" spans="1:10" ht="15.95"/>
+    <row r="135" spans="1:10" ht="15.95">
       <c r="A135" s="11"/>
       <c r="C135" s="6"/>
       <c r="G135" s="1"/>
@@ -6002,23 +5995,23 @@
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" ht="15.95">
       <c r="A136" s="11"/>
       <c r="C136" s="11"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" ht="15.95">
       <c r="A137" s="11"/>
       <c r="C137" s="11"/>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" ht="15.95">
       <c r="A138" s="11"/>
       <c r="C138" s="11"/>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" ht="15.95">
       <c r="A139" s="11"/>
       <c r="C139" s="11"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" ht="15.95">
       <c r="A140" s="11"/>
     </row>
   </sheetData>
@@ -6058,16 +6051,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="33.950000000000003">
@@ -6081,18 +6074,18 @@
         <v>2500</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -6107,18 +6100,18 @@
         <v>2500</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -6133,16 +6126,16 @@
         <v>184000</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -6157,16 +6150,16 @@
         <v>1140375</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="J5" s="1"/>
     </row>
@@ -6181,18 +6174,18 @@
         <v>2500</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -6207,18 +6200,18 @@
         <v>25000</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="J7" s="1"/>
     </row>
@@ -6233,16 +6226,16 @@
         <v>2500</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -6257,16 +6250,16 @@
         <v>300000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -6281,16 +6274,16 @@
         <v>30000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -6305,16 +6298,16 @@
         <v>80000</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J11" s="1"/>
     </row>
@@ -6329,16 +6322,16 @@
         <v>5000</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="1"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J12" s="1"/>
     </row>
@@ -6353,18 +6346,18 @@
         <v>1300000</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J13" s="1"/>
     </row>
@@ -6379,16 +6372,16 @@
         <v>44000</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J14" s="1"/>
     </row>
@@ -6403,16 +6396,16 @@
         <v>840000</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -6427,18 +6420,18 @@
         <v>2500</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -6453,16 +6446,16 @@
         <v>32500</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J17" s="1"/>
     </row>
@@ -6477,18 +6470,18 @@
         <v>20100</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -6503,16 +6496,16 @@
         <v>60000</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -6527,16 +6520,16 @@
         <v>40000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J20" s="1"/>
     </row>
@@ -6551,16 +6544,16 @@
         <v>18000</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J21" s="1"/>
     </row>
@@ -6575,14 +6568,14 @@
         <v>500000</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="J22" s="1"/>
     </row>
@@ -6597,16 +6590,16 @@
         <v>20000</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -6621,16 +6614,16 @@
         <v>25000</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="J24" s="1"/>
     </row>
@@ -6645,16 +6638,16 @@
         <v>25000</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="J25" s="1"/>
     </row>
@@ -6669,18 +6662,18 @@
         <v>2500</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J26" s="1"/>
     </row>
@@ -6695,16 +6688,16 @@
         <v>90000</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J27" s="1"/>
     </row>
@@ -6719,14 +6712,14 @@
         <v>10000</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J28" s="1"/>
     </row>
@@ -6741,14 +6734,14 @@
         <v>200000</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J29" s="1"/>
     </row>
@@ -6763,18 +6756,18 @@
         <v>2500</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J30" s="1"/>
     </row>
@@ -6789,16 +6782,16 @@
         <v>500000</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J31" s="1"/>
     </row>
@@ -6813,14 +6806,14 @@
         <v>14000</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="23"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="J32" s="1"/>
     </row>
@@ -6835,14 +6828,14 @@
         <v>150000</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="6"/>
       <c r="G33" s="23"/>
       <c r="H33" s="1"/>
       <c r="I33" s="6" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="J33" s="1"/>
     </row>
@@ -6857,14 +6850,14 @@
         <v>25000</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="6" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J34" s="1"/>
     </row>
@@ -6879,16 +6872,16 @@
         <v>45000</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="6" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="1"/>
       <c r="I35" s="6" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J35" s="1"/>
     </row>
@@ -6903,16 +6896,16 @@
         <v>500000</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="1"/>
       <c r="I36" s="6" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="J36" s="1"/>
     </row>
@@ -6927,18 +6920,18 @@
         <v>2500</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="1"/>
       <c r="I37" s="6" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="J37" s="1"/>
     </row>
@@ -6953,14 +6946,14 @@
         <v>150000</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
       <c r="G38" s="23"/>
       <c r="H38" s="1"/>
       <c r="I38" s="6" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="J38" s="1"/>
     </row>
@@ -6975,16 +6968,16 @@
         <v>100000</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G39" s="23"/>
       <c r="H39" s="1"/>
       <c r="I39" s="6" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="J39" s="1"/>
     </row>
@@ -6999,16 +6992,16 @@
         <v>2500</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E40" s="25"/>
       <c r="F40" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G40" s="23"/>
       <c r="H40" s="1"/>
       <c r="I40" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J40" s="1"/>
     </row>
@@ -7023,16 +7016,16 @@
         <v>10000</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="23"/>
       <c r="H41" s="1"/>
       <c r="I41" s="6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="J41" s="1"/>
     </row>
@@ -7047,14 +7040,14 @@
         <v>920000</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J42" s="1"/>
     </row>
@@ -7069,18 +7062,18 @@
         <v>2500</v>
       </c>
       <c r="D43" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="25" t="s">
-        <v>39</v>
-      </c>
       <c r="F43" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="6" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J43" s="1"/>
     </row>
@@ -7095,16 +7088,16 @@
         <v>45000</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="6" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="6" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J44" s="1"/>
     </row>
@@ -7119,16 +7112,16 @@
         <v>180000</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="6" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="J45" s="1"/>
     </row>
@@ -7143,14 +7136,14 @@
         <v>2250</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -7165,16 +7158,16 @@
         <v>860000</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="6" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -7189,16 +7182,16 @@
         <v>1000</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -7213,14 +7206,14 @@
         <v>2000</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="6"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="J49" s="1"/>
     </row>
@@ -7235,18 +7228,18 @@
         <v>150000</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="6" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="J50" s="1"/>
     </row>
@@ -7261,18 +7254,18 @@
         <v>3000</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J51" s="1"/>
     </row>
@@ -7287,18 +7280,18 @@
         <v>2500</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J52" s="1"/>
     </row>
@@ -7313,16 +7306,16 @@
         <v>12000</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="11" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J53" s="5"/>
     </row>
@@ -7337,16 +7330,16 @@
         <v>67000</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="11" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J54" s="5"/>
     </row>
@@ -7361,16 +7354,16 @@
         <v>75000</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="11" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J55" s="5"/>
     </row>
@@ -7385,14 +7378,14 @@
         <v>300000</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="11"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="11" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J56" s="5"/>
     </row>
@@ -7407,16 +7400,16 @@
         <v>300000</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="11" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="11" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="J57" s="5"/>
     </row>
@@ -7431,18 +7424,18 @@
         <v>7500</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="11" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J58" s="5"/>
     </row>
@@ -7457,16 +7450,16 @@
         <v>24000</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="26" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J59" s="5"/>
     </row>
@@ -7481,16 +7474,16 @@
         <v>750000</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="11" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="J60" s="5"/>
     </row>
@@ -7505,16 +7498,16 @@
         <v>9000</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="11" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J61" s="5"/>
     </row>
@@ -7531,12 +7524,12 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="11" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="J62" s="5"/>
     </row>
@@ -7552,13 +7545,13 @@
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="11" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="J63" s="5"/>
     </row>
@@ -7575,12 +7568,12 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="J64" s="5"/>
     </row>
@@ -7597,12 +7590,12 @@
       <c r="D65" s="37"/>
       <c r="E65" s="37"/>
       <c r="F65" s="37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G65" s="37"/>
       <c r="H65" s="37"/>
       <c r="I65" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J65" s="5"/>
     </row>
@@ -7658,12 +7651,12 @@
       <c r="A70" s="11"/>
       <c r="B70" s="13"/>
       <c r="C70" s="14"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="56"/>
+      <c r="G70" s="56"/>
+      <c r="H70" s="56"/>
+      <c r="I70" s="56"/>
       <c r="J70" s="5"/>
     </row>
     <row r="71" spans="1:10">
@@ -7683,7 +7676,7 @@
       <c r="B72" s="13"/>
       <c r="C72" s="14"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="42"/>
+      <c r="E72" s="41"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -7743,7 +7736,7 @@
       <c r="B77" s="13"/>
       <c r="C77" s="24"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="42"/>
+      <c r="E77" s="41"/>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -7946,12 +7939,12 @@
       <c r="A94" s="11"/>
       <c r="B94" s="13"/>
       <c r="C94" s="14"/>
-      <c r="D94" s="59"/>
-      <c r="E94" s="59"/>
-      <c r="F94" s="59"/>
-      <c r="G94" s="59"/>
-      <c r="H94" s="59"/>
-      <c r="I94" s="59"/>
+      <c r="D94" s="58"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="58"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="58"/>
+      <c r="I94" s="58"/>
       <c r="J94" s="11"/>
     </row>
     <row r="95" spans="1:10">
@@ -7971,7 +7964,7 @@
       <c r="B96" s="13"/>
       <c r="C96" s="14"/>
       <c r="D96" s="13"/>
-      <c r="E96" s="42"/>
+      <c r="E96" s="41"/>
       <c r="F96" s="11"/>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
@@ -8156,7 +8149,7 @@
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
-      <c r="J111" s="47"/>
+      <c r="J111" s="46"/>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="6"/>
@@ -8204,7 +8197,7 @@
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
-      <c r="J115" s="47"/>
+      <c r="J115" s="46"/>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="6"/>
@@ -8259,7 +8252,7 @@
       <c r="B120" s="6"/>
       <c r="C120" s="2"/>
       <c r="D120" s="6"/>
-      <c r="E120" s="42"/>
+      <c r="E120" s="41"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
@@ -8271,7 +8264,7 @@
       <c r="B121" s="6"/>
       <c r="C121" s="2"/>
       <c r="D121" s="6"/>
-      <c r="E121" s="42"/>
+      <c r="E121" s="41"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
@@ -8307,7 +8300,7 @@
       <c r="B124" s="6"/>
       <c r="C124" s="2"/>
       <c r="D124" s="11"/>
-      <c r="E124" s="42"/>
+      <c r="E124" s="41"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
@@ -8343,7 +8336,7 @@
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
       <c r="D127" s="6"/>
-      <c r="E127" s="42"/>
+      <c r="E127" s="41"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
@@ -8355,7 +8348,7 @@
       <c r="B128" s="6"/>
       <c r="C128" s="2"/>
       <c r="D128" s="6"/>
-      <c r="E128" s="42"/>
+      <c r="E128" s="41"/>
       <c r="F128" s="6"/>
       <c r="G128" s="2"/>
       <c r="H128" s="6"/>
@@ -8367,7 +8360,7 @@
       <c r="B129" s="6"/>
       <c r="C129" s="2"/>
       <c r="D129" s="6"/>
-      <c r="E129" s="42"/>
+      <c r="E129" s="41"/>
       <c r="F129" s="6"/>
       <c r="G129" s="2"/>
       <c r="H129" s="6"/>
@@ -8379,7 +8372,7 @@
       <c r="B130" s="6"/>
       <c r="C130" s="2"/>
       <c r="D130" s="6"/>
-      <c r="E130" s="42"/>
+      <c r="E130" s="41"/>
       <c r="F130" s="6"/>
       <c r="G130" s="2"/>
       <c r="H130" s="6"/>
@@ -8391,7 +8384,7 @@
       <c r="B131" s="6"/>
       <c r="C131" s="2"/>
       <c r="D131" s="6"/>
-      <c r="E131" s="42"/>
+      <c r="E131" s="41"/>
       <c r="F131" s="6"/>
       <c r="G131" s="2"/>
       <c r="H131" s="6"/>
@@ -8402,24 +8395,24 @@
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="60"/>
-      <c r="E132" s="60"/>
-      <c r="F132" s="60"/>
-      <c r="G132" s="61"/>
-      <c r="H132" s="60"/>
-      <c r="I132" s="60"/>
+      <c r="D132" s="59"/>
+      <c r="E132" s="59"/>
+      <c r="F132" s="59"/>
+      <c r="G132" s="60"/>
+      <c r="H132" s="59"/>
+      <c r="I132" s="59"/>
       <c r="J132" s="6"/>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="60"/>
-      <c r="E133" s="60"/>
-      <c r="F133" s="60"/>
-      <c r="G133" s="61"/>
-      <c r="H133" s="60"/>
-      <c r="I133" s="60"/>
+      <c r="D133" s="59"/>
+      <c r="E133" s="59"/>
+      <c r="F133" s="59"/>
+      <c r="G133" s="60"/>
+      <c r="H133" s="59"/>
+      <c r="I133" s="59"/>
       <c r="J133" s="6"/>
     </row>
     <row r="134" spans="1:10">
@@ -8427,11 +8420,11 @@
       <c r="B134" s="6"/>
       <c r="C134" s="2"/>
       <c r="D134" s="6"/>
-      <c r="E134" s="60"/>
+      <c r="E134" s="59"/>
       <c r="F134" s="6"/>
       <c r="G134" s="2"/>
-      <c r="H134" s="60"/>
-      <c r="I134" s="60"/>
+      <c r="H134" s="59"/>
+      <c r="I134" s="59"/>
       <c r="J134" s="6"/>
     </row>
   </sheetData>
@@ -8441,924 +8434,1161 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480C634D-F797-FB45-A84D-160F0A67B3F9}">
-  <dimension ref="A1:D90"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E140"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="29.5" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="33.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="39.950000000000003">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="109" t="s">
-        <v>366</v>
-      </c>
-      <c r="D1" s="110" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="C1" s="115" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1" s="115" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.100000000000001">
       <c r="A2" s="11">
         <v>2015</v>
       </c>
       <c r="B2" s="14">
         <v>4000</v>
       </c>
-      <c r="C2" s="111" t="s">
-        <v>368</v>
-      </c>
-      <c r="D2" s="110"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.100000000000001">
       <c r="A3" s="11">
         <v>2015</v>
       </c>
       <c r="B3" s="14">
         <v>50000</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="110"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" ht="17.100000000000001">
       <c r="A4" s="11">
         <v>2015</v>
       </c>
       <c r="B4" s="14">
         <v>225000</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="110"/>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="17.100000000000001">
       <c r="A5" s="11">
         <v>2015</v>
       </c>
       <c r="B5" s="14">
         <v>337600</v>
       </c>
-      <c r="C5" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="110"/>
-    </row>
-    <row r="6" spans="1:4" ht="28.5">
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.100000000000001">
       <c r="A6" s="11">
         <v>2015</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="14">
         <v>400000</v>
       </c>
-      <c r="C6" s="114" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="110"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="117" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="17.100000000000001">
       <c r="A7" s="11">
         <v>2016</v>
       </c>
       <c r="B7" s="14">
         <v>450000</v>
       </c>
-      <c r="C7" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="110"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="11">
         <v>2016</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="14">
         <v>78000</v>
       </c>
-      <c r="C8" s="116" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="110"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="17.100000000000001">
       <c r="A9" s="11">
         <v>2016</v>
       </c>
       <c r="B9" s="14">
         <v>717246</v>
       </c>
-      <c r="C9" s="117" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="110"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="C9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="17.100000000000001">
       <c r="A10" s="11">
         <v>2016</v>
       </c>
       <c r="B10" s="14">
         <v>180000</v>
       </c>
-      <c r="C10" s="118" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="110"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="C10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="17.100000000000001">
       <c r="A11" s="11">
         <v>2016</v>
       </c>
       <c r="B11" s="24">
         <v>50000</v>
       </c>
-      <c r="C11" s="118" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="110"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="C11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.100000000000001">
       <c r="A12" s="11">
         <v>2016</v>
       </c>
-      <c r="B12" s="106">
+      <c r="B12" s="24">
         <v>24000</v>
       </c>
-      <c r="C12" s="119" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="110"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="C12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="11">
         <v>2016</v>
       </c>
       <c r="B13" s="24">
         <v>4000</v>
       </c>
-      <c r="C13" s="120" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="110"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="C13" s="118" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.100000000000001">
       <c r="A14" s="11">
         <v>2016</v>
       </c>
       <c r="B14" s="24">
         <v>75900</v>
       </c>
-      <c r="C14" s="89" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="110" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="C14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="17.100000000000001">
       <c r="A15" s="11">
         <v>2017</v>
       </c>
       <c r="B15" s="14">
         <v>7500</v>
       </c>
-      <c r="C15" s="111" t="s">
+      <c r="C15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="110"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="17.100000000000001">
       <c r="A16" s="11">
         <v>2017</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="14">
         <v>65000</v>
       </c>
-      <c r="C16" s="116" t="s">
+      <c r="C16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="110"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" ht="17.100000000000001">
       <c r="A17" s="11">
         <v>2018</v>
       </c>
       <c r="B17" s="14">
         <v>45000</v>
       </c>
-      <c r="C17" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="110" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="C17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" ht="17.100000000000001">
       <c r="A18" s="11">
         <v>2018</v>
       </c>
       <c r="B18" s="14">
         <v>300000</v>
       </c>
-      <c r="C18" s="118" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="110" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="C18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" ht="17.100000000000001">
       <c r="A19" s="11">
         <v>2018</v>
       </c>
       <c r="B19" s="14">
         <v>558242</v>
       </c>
-      <c r="C19" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="122"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="C19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="119"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5" ht="17.100000000000001">
       <c r="A20" s="11">
         <v>2018</v>
       </c>
       <c r="B20" s="14">
         <v>66000</v>
       </c>
-      <c r="C20" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="122"/>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="119"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" ht="17.100000000000001">
       <c r="A21" s="11">
         <v>2018</v>
       </c>
       <c r="B21" s="14">
         <v>579703</v>
       </c>
-      <c r="C21" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="122"/>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="C21" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="119"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:5" ht="17.100000000000001">
       <c r="A22" s="11">
         <v>2018</v>
       </c>
       <c r="B22" s="14">
         <v>546017</v>
       </c>
-      <c r="C22" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="122"/>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="C22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="119"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="1:5" ht="17.100000000000001">
       <c r="A23" s="11">
         <v>2018</v>
       </c>
       <c r="B23" s="14">
         <v>60000</v>
       </c>
-      <c r="C23" s="115" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="122"/>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="C23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="119"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:5" ht="17.100000000000001">
       <c r="A24" s="11">
         <v>2019</v>
       </c>
       <c r="B24" s="14">
         <v>24765</v>
       </c>
-      <c r="C24" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="122"/>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="C24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="119"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" ht="17.100000000000001">
       <c r="A25" s="11">
         <v>2019</v>
       </c>
       <c r="B25" s="14">
         <v>15000</v>
       </c>
-      <c r="C25" s="117" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="122" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="C25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="119" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" ht="17.100000000000001">
       <c r="A26" s="11">
         <v>2019</v>
       </c>
       <c r="B26" s="14">
         <v>120000</v>
       </c>
-      <c r="C26" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="124"/>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="C26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="120"/>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:5" ht="17.100000000000001">
       <c r="A27" s="11">
         <v>2019</v>
       </c>
       <c r="B27" s="14">
         <v>150000</v>
       </c>
-      <c r="C27" s="125" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="126"/>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="C27" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:5" ht="17.100000000000001">
       <c r="A28" s="11">
         <v>2019</v>
       </c>
       <c r="B28" s="14">
         <v>300000</v>
       </c>
-      <c r="C28" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="110"/>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="C28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" spans="1:5" ht="17.100000000000001">
       <c r="A29" s="11">
         <v>2019</v>
       </c>
       <c r="B29" s="14">
         <v>90000</v>
       </c>
-      <c r="C29" s="127" t="s">
+      <c r="C29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="126"/>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" spans="1:5" ht="17.100000000000001">
       <c r="A30" s="11">
         <v>2019</v>
       </c>
       <c r="B30" s="14">
         <v>627100</v>
       </c>
-      <c r="C30" s="125" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="126"/>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="C30" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" spans="1:5" ht="17.100000000000001">
       <c r="A31" s="11">
         <v>2020</v>
       </c>
-      <c r="B31" s="56">
+      <c r="B31" s="14">
         <v>25000</v>
       </c>
-      <c r="C31" s="119" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="122"/>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="C31" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="119"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:5" ht="17.100000000000001">
       <c r="A32" s="11">
         <v>2020</v>
       </c>
       <c r="B32" s="14">
         <v>9000</v>
       </c>
-      <c r="C32" s="120" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="124"/>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="C32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="120"/>
+      <c r="E32" s="11"/>
+    </row>
+    <row r="33" spans="1:5" ht="17.100000000000001">
       <c r="A33" s="11">
         <v>2020</v>
       </c>
       <c r="B33" s="14">
         <v>7500</v>
       </c>
-      <c r="C33" s="111" t="s">
+      <c r="C33" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="124"/>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="D33" s="120"/>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34" spans="1:5" ht="17.100000000000001">
       <c r="A34" s="11">
         <v>2020</v>
       </c>
       <c r="B34" s="14">
         <v>592822</v>
       </c>
-      <c r="C34" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="124"/>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="C34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="11"/>
+    </row>
+    <row r="35" spans="1:5" ht="17.100000000000001">
       <c r="A35" s="11">
         <v>2020</v>
       </c>
       <c r="B35" s="14">
         <v>384000</v>
       </c>
-      <c r="C35" s="123" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="124"/>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="C35" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="120"/>
+      <c r="E35" s="11"/>
+    </row>
+    <row r="36" spans="1:5" ht="17.100000000000001">
       <c r="A36" s="11">
         <v>2020</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="2">
         <v>500000</v>
       </c>
-      <c r="C36" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="124"/>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="C36" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="120"/>
+      <c r="E36" s="11"/>
+    </row>
+    <row r="37" spans="1:5" ht="17.100000000000001">
       <c r="A37" s="11">
         <v>2020</v>
       </c>
-      <c r="B37" s="56">
+      <c r="B37" s="14">
         <v>210000</v>
       </c>
-      <c r="C37" s="128" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" s="124"/>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="C37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="120" t="s">
+        <v>363</v>
+      </c>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" spans="1:5" ht="17.100000000000001">
       <c r="A38" s="11">
         <v>2020</v>
       </c>
       <c r="B38" s="14">
         <v>59560</v>
       </c>
-      <c r="C38" s="127" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" s="126"/>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="C38" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:5" ht="17.100000000000001">
       <c r="A39" s="11">
         <v>2020</v>
       </c>
       <c r="B39" s="14">
         <v>98000</v>
       </c>
-      <c r="C39" s="127" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="126"/>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="C39" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:5" ht="17.100000000000001">
       <c r="A40" s="11">
         <v>2021</v>
       </c>
       <c r="B40" s="14">
         <v>578684</v>
       </c>
-      <c r="C40" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="126"/>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="C40" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:5" ht="17.100000000000001">
       <c r="A41" s="11">
         <v>2021</v>
       </c>
       <c r="B41" s="14">
         <v>200000</v>
       </c>
-      <c r="C41" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" s="110"/>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="C41" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" ht="17.100000000000001">
       <c r="A42" s="11">
         <v>2022</v>
       </c>
       <c r="B42" s="14">
         <v>30000</v>
       </c>
-      <c r="C42" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="126"/>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="C42" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:5" ht="17.100000000000001">
       <c r="A43" s="11">
         <v>2022</v>
       </c>
       <c r="B43" s="14">
         <v>539125</v>
       </c>
-      <c r="C43" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="126"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="11">
+      <c r="C43" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="44" spans="1:5" ht="17.100000000000001">
+      <c r="A44" s="6">
         <v>2020</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="2">
         <v>99995</v>
       </c>
-      <c r="C44" s="131" t="s">
-        <v>128</v>
-      </c>
-      <c r="D44" s="126"/>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="11">
+      <c r="C44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="1:5" ht="17.100000000000001">
+      <c r="A45" s="6">
         <v>2020</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="2">
         <v>15000</v>
       </c>
-      <c r="C45" s="111" t="s">
+      <c r="C45" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D45" s="126"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="11">
+      <c r="D45" s="11"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:5" ht="17.100000000000001">
+      <c r="A46" s="6">
         <v>2020</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="2">
         <v>98000</v>
       </c>
-      <c r="C46" s="127" t="s">
+      <c r="C46" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="126"/>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="11">
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+    </row>
+    <row r="47" spans="1:5" ht="17.100000000000001">
+      <c r="A47" s="6">
         <v>2020</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="2">
         <v>500000</v>
       </c>
-      <c r="C47" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D47" s="126"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="11">
+      <c r="C47" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+    </row>
+    <row r="48" spans="1:5" ht="17.100000000000001">
+      <c r="A48" s="6">
         <v>2020</v>
       </c>
-      <c r="B48" s="56">
+      <c r="B48" s="2">
         <v>55000</v>
       </c>
-      <c r="C48" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" s="126"/>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="11">
+      <c r="C48" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" spans="1:5" ht="17.100000000000001">
+      <c r="A49" s="6">
         <v>2020</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="2">
         <v>75000</v>
       </c>
-      <c r="C49" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" s="126"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="11">
+      <c r="C49" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="11"/>
+    </row>
+    <row r="50" spans="1:5" ht="17.100000000000001">
+      <c r="A50" s="6">
         <v>2020</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="2">
         <v>340554</v>
       </c>
-      <c r="C50" s="130" t="s">
-        <v>155</v>
-      </c>
-      <c r="D50" s="126"/>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="11">
+      <c r="C50" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="11"/>
+    </row>
+    <row r="51" spans="1:5" ht="17.100000000000001">
+      <c r="A51" s="6">
         <v>2020</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="2">
         <v>548725</v>
       </c>
-      <c r="C51" s="128" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="126"/>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="11">
+      <c r="C51" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="E51" s="5"/>
+    </row>
+    <row r="52" spans="1:5" ht="17.100000000000001">
+      <c r="A52" s="6">
         <v>2021</v>
       </c>
-      <c r="B52" s="56">
+      <c r="B52" s="7">
         <v>200000</v>
       </c>
-      <c r="C52" s="132" t="s">
-        <v>166</v>
-      </c>
-      <c r="D52" s="126"/>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="11">
+      <c r="C52" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+    </row>
+    <row r="53" spans="1:5" ht="17.100000000000001">
+      <c r="A53" s="6">
         <v>2021</v>
       </c>
-      <c r="B53" s="107">
+      <c r="B53" s="4">
         <v>9941</v>
       </c>
-      <c r="C53" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="126"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="11">
+      <c r="C53" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+    </row>
+    <row r="54" spans="1:5" ht="17.100000000000001">
+      <c r="A54" s="6">
         <v>2021</v>
       </c>
-      <c r="B54" s="107">
+      <c r="B54" s="4">
         <v>69956</v>
       </c>
-      <c r="C54" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" s="126"/>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="11">
+      <c r="C54" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+    </row>
+    <row r="55" spans="1:5" ht="17.100000000000001">
+      <c r="A55" s="6">
         <v>2023</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="2">
         <v>9000</v>
       </c>
-      <c r="C55" s="111" t="s">
+      <c r="C55" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D55" s="126"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="11">
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+    </row>
+    <row r="56" spans="1:5" ht="17.100000000000001">
+      <c r="A56" s="6">
         <v>2023</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="2">
         <v>750000</v>
       </c>
-      <c r="C56" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D56" s="126"/>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="11">
+      <c r="C56" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="11"/>
+      <c r="E56" s="5"/>
+    </row>
+    <row r="57" spans="1:5" ht="17.100000000000001">
+      <c r="A57" s="6">
         <v>2023</v>
       </c>
-      <c r="B57" s="14">
+      <c r="B57" s="2">
         <v>700000</v>
       </c>
-      <c r="C57" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D57" s="126"/>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="11">
+      <c r="C57" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="5"/>
+    </row>
+    <row r="58" spans="1:5" ht="17.100000000000001">
+      <c r="A58" s="6">
         <v>2023</v>
       </c>
-      <c r="B58" s="14">
+      <c r="B58" s="2">
         <v>46000</v>
       </c>
-      <c r="C58" s="127" t="s">
+      <c r="C58" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="126"/>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="11">
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+    </row>
+    <row r="59" spans="1:5" ht="17.100000000000001">
+      <c r="A59" s="6">
         <v>2023</v>
       </c>
-      <c r="B59" s="14">
+      <c r="B59" s="2">
         <v>46000</v>
       </c>
-      <c r="C59" s="127" t="s">
+      <c r="C59" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="126"/>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="11">
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+    </row>
+    <row r="60" spans="1:5" ht="17.100000000000001">
+      <c r="A60" s="6">
         <v>2023</v>
       </c>
-      <c r="B60" s="14">
+      <c r="B60" s="2">
         <v>748339</v>
       </c>
-      <c r="C60" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D60" s="126"/>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="11">
+      <c r="C60" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D60" s="11"/>
+      <c r="E60" s="5"/>
+    </row>
+    <row r="61" spans="1:5" ht="17.100000000000001">
+      <c r="A61" s="6">
         <v>2024</v>
       </c>
-      <c r="B61" s="14">
+      <c r="B61" s="2">
         <v>46000</v>
       </c>
-      <c r="C61" s="127" t="s">
+      <c r="C61" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D61" s="126"/>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="11">
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+    </row>
+    <row r="62" spans="1:5" ht="17.100000000000001">
+      <c r="A62" s="6">
         <v>2024</v>
       </c>
-      <c r="B62" s="14">
+      <c r="B62" s="2">
         <v>46000</v>
       </c>
-      <c r="C62" s="127" t="s">
+      <c r="C62" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D62" s="126"/>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="11">
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+    </row>
+    <row r="63" spans="1:5" ht="17.100000000000001">
+      <c r="A63" s="6">
         <v>2024</v>
       </c>
-      <c r="B63" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="C63" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="126"/>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="11">
+      <c r="B63" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" s="11"/>
+      <c r="E63" s="5"/>
+    </row>
+    <row r="64" spans="1:5" ht="17.100000000000001">
+      <c r="A64" s="6">
         <v>2024</v>
       </c>
-      <c r="B64" s="14">
+      <c r="B64" s="2">
         <v>43272</v>
       </c>
-      <c r="C64" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D64" s="126"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="11">
+      <c r="C64" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" s="11"/>
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65" spans="1:5" ht="17.100000000000001">
+      <c r="A65" s="6">
         <v>2024</v>
       </c>
-      <c r="B65" s="14">
+      <c r="B65" s="2">
         <v>75000</v>
       </c>
-      <c r="C65" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D65" s="126"/>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="11">
+      <c r="C65" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="5"/>
+    </row>
+    <row r="66" spans="1:5" ht="17.100000000000001">
+      <c r="A66" s="6">
         <v>2024</v>
       </c>
-      <c r="B66" s="14">
+      <c r="B66" s="2">
         <v>800000</v>
       </c>
-      <c r="C66" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D66" s="126"/>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="11">
+      <c r="C66" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D66" s="11"/>
+      <c r="E66" s="5"/>
+    </row>
+    <row r="67" spans="1:5" ht="17.100000000000001">
+      <c r="A67" s="6">
         <v>2024</v>
       </c>
-      <c r="B67" s="14">
+      <c r="B67" s="2">
         <v>186789</v>
       </c>
-      <c r="C67" s="133" t="s">
-        <v>186</v>
-      </c>
-      <c r="D67" s="126"/>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="11">
+      <c r="C67" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="5"/>
+    </row>
+    <row r="68" spans="1:5" ht="17.100000000000001">
+      <c r="A68" s="6">
         <v>2024</v>
       </c>
-      <c r="B68" s="14">
+      <c r="B68" s="2">
         <v>997450</v>
       </c>
-      <c r="C68" s="125" t="s">
-        <v>53</v>
-      </c>
-      <c r="D68" s="126"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="11">
+      <c r="C68" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+    </row>
+    <row r="69" spans="1:5" ht="17.100000000000001">
+      <c r="A69" s="6">
         <v>2024</v>
       </c>
-      <c r="B69" s="14">
+      <c r="B69" s="2">
         <v>1000000</v>
       </c>
-      <c r="C69" s="125" t="s">
-        <v>53</v>
-      </c>
-      <c r="D69" s="126"/>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="11">
+      <c r="C69" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+    </row>
+    <row r="70" spans="1:5" ht="17.100000000000001">
+      <c r="A70" s="6">
         <v>2024</v>
       </c>
-      <c r="B70" s="14">
+      <c r="B70" s="2">
         <v>500000</v>
       </c>
-      <c r="C70" s="127" t="s">
-        <v>234</v>
-      </c>
-      <c r="D70" s="126"/>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="C71" s="134"/>
-      <c r="D71" s="134"/>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="D72" s="108"/>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="D73" s="108"/>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="D74" s="108"/>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="D75" s="108"/>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="D76" s="108"/>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="D77" s="108"/>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="D78" s="108"/>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="D79" s="108"/>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="D80" s="108"/>
-    </row>
-    <row r="81" spans="4:4">
-      <c r="D81" s="108"/>
-    </row>
-    <row r="82" spans="4:4">
-      <c r="D82" s="108"/>
-    </row>
-    <row r="83" spans="4:4">
-      <c r="D83" s="108"/>
-    </row>
-    <row r="84" spans="4:4">
-      <c r="D84" s="108"/>
-    </row>
-    <row r="85" spans="4:4">
-      <c r="D85" s="108"/>
-    </row>
-    <row r="86" spans="4:4">
-      <c r="D86" s="108"/>
-    </row>
-    <row r="87" spans="4:4">
-      <c r="D87" s="108"/>
-    </row>
-    <row r="88" spans="4:4">
-      <c r="D88" s="108"/>
-    </row>
-    <row r="89" spans="4:4">
-      <c r="D89" s="108"/>
-    </row>
-    <row r="90" spans="4:4">
-      <c r="D90" s="108"/>
+      <c r="C70" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" s="5"/>
+    </row>
+    <row r="71" spans="1:5" ht="18.95">
+      <c r="A71" s="106"/>
+      <c r="B71" s="106"/>
+      <c r="C71" s="116"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="5"/>
+    </row>
+    <row r="72" spans="1:5" ht="18.95">
+      <c r="A72" s="106"/>
+      <c r="B72" s="106"/>
+      <c r="C72" s="116"/>
+      <c r="D72" s="116"/>
+      <c r="E72" s="5"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="E73" s="5"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="E74" s="5"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="E75" s="5"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="E76" s="5"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="E77" s="5"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="E78" s="5"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="E79" s="5"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="E80" s="5"/>
+    </row>
+    <row r="81" spans="5:5">
+      <c r="E81" s="5"/>
+    </row>
+    <row r="82" spans="5:5">
+      <c r="E82" s="5"/>
+    </row>
+    <row r="83" spans="5:5">
+      <c r="E83" s="5"/>
+    </row>
+    <row r="84" spans="5:5">
+      <c r="E84" s="5"/>
+    </row>
+    <row r="85" spans="5:5">
+      <c r="E85" s="5"/>
+    </row>
+    <row r="86" spans="5:5">
+      <c r="E86" s="5"/>
+    </row>
+    <row r="87" spans="5:5">
+      <c r="E87" s="5"/>
+    </row>
+    <row r="88" spans="5:5">
+      <c r="E88" s="5"/>
+    </row>
+    <row r="89" spans="5:5">
+      <c r="E89" s="5"/>
+    </row>
+    <row r="90" spans="5:5">
+      <c r="E90" s="5"/>
+    </row>
+    <row r="91" spans="5:5">
+      <c r="E91" s="5"/>
+    </row>
+    <row r="92" spans="5:5">
+      <c r="E92" s="5"/>
+    </row>
+    <row r="93" spans="5:5">
+      <c r="E93" s="5"/>
+    </row>
+    <row r="94" spans="5:5">
+      <c r="E94" s="5"/>
+    </row>
+    <row r="95" spans="5:5">
+      <c r="E95" s="5"/>
+    </row>
+    <row r="96" spans="5:5">
+      <c r="E96" s="5"/>
+    </row>
+    <row r="97" spans="5:5">
+      <c r="E97" s="5"/>
+    </row>
+    <row r="98" spans="5:5">
+      <c r="E98" s="5"/>
+    </row>
+    <row r="99" spans="5:5">
+      <c r="E99" s="5"/>
+    </row>
+    <row r="100" spans="5:5">
+      <c r="E100" s="5"/>
+    </row>
+    <row r="101" spans="5:5">
+      <c r="E101" s="5"/>
+    </row>
+    <row r="102" spans="5:5">
+      <c r="E102" s="5"/>
+    </row>
+    <row r="103" spans="5:5">
+      <c r="E103" s="5"/>
+    </row>
+    <row r="104" spans="5:5">
+      <c r="E104" s="5"/>
+    </row>
+    <row r="105" spans="5:5">
+      <c r="E105" s="5"/>
+    </row>
+    <row r="106" spans="5:5">
+      <c r="E106" s="5"/>
+    </row>
+    <row r="107" spans="5:5">
+      <c r="E107" s="5"/>
+    </row>
+    <row r="108" spans="5:5">
+      <c r="E108" s="5"/>
+    </row>
+    <row r="109" spans="5:5">
+      <c r="E109" s="5"/>
+    </row>
+    <row r="110" spans="5:5">
+      <c r="E110" s="5"/>
+    </row>
+    <row r="111" spans="5:5">
+      <c r="E111" s="5"/>
+    </row>
+    <row r="112" spans="5:5">
+      <c r="E112" s="5"/>
+    </row>
+    <row r="113" spans="5:5">
+      <c r="E113" s="5"/>
+    </row>
+    <row r="114" spans="5:5">
+      <c r="E114" s="5"/>
+    </row>
+    <row r="115" spans="5:5">
+      <c r="E115" s="5"/>
+    </row>
+    <row r="116" spans="5:5">
+      <c r="E116" s="5"/>
+    </row>
+    <row r="117" spans="5:5">
+      <c r="E117" s="5"/>
+    </row>
+    <row r="118" spans="5:5">
+      <c r="E118" s="5"/>
+    </row>
+    <row r="119" spans="5:5">
+      <c r="E119" s="5"/>
+    </row>
+    <row r="120" spans="5:5">
+      <c r="E120" s="5"/>
+    </row>
+    <row r="121" spans="5:5">
+      <c r="E121" s="5"/>
+    </row>
+    <row r="122" spans="5:5">
+      <c r="E122" s="5"/>
+    </row>
+    <row r="123" spans="5:5">
+      <c r="E123" s="5"/>
+    </row>
+    <row r="124" spans="5:5">
+      <c r="E124" s="5"/>
+    </row>
+    <row r="125" spans="5:5">
+      <c r="E125" s="5"/>
+    </row>
+    <row r="126" spans="5:5">
+      <c r="E126" s="5"/>
+    </row>
+    <row r="127" spans="5:5">
+      <c r="E127" s="5"/>
+    </row>
+    <row r="128" spans="5:5">
+      <c r="E128" s="5"/>
+    </row>
+    <row r="129" spans="5:5">
+      <c r="E129" s="5"/>
+    </row>
+    <row r="130" spans="5:5">
+      <c r="E130" s="5"/>
+    </row>
+    <row r="131" spans="5:5">
+      <c r="E131" s="5"/>
+    </row>
+    <row r="132" spans="5:5">
+      <c r="E132" s="5"/>
+    </row>
+    <row r="133" spans="5:5">
+      <c r="E133" s="5"/>
+    </row>
+    <row r="134" spans="5:5">
+      <c r="E134" s="5"/>
+    </row>
+    <row r="135" spans="5:5">
+      <c r="E135" s="1"/>
+    </row>
+    <row r="136" spans="5:5">
+      <c r="E136" s="5"/>
+    </row>
+    <row r="137" spans="5:5">
+      <c r="E137" s="5"/>
+    </row>
+    <row r="138" spans="5:5">
+      <c r="E138" s="5"/>
+    </row>
+    <row r="139" spans="5:5">
+      <c r="E139" s="5"/>
+    </row>
+    <row r="140" spans="5:5">
+      <c r="E140" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1740CAF.xlsx
+++ b/1740CAF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lan74_pitt_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2978696C-1EE7-48BA-AA78-26FBAA5F5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{679645A4-519C-42B3-89C6-BF342277225F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5540" yWindow="760" windowWidth="23260" windowHeight="16260" firstSheet="2" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
@@ -259,7 +259,7 @@
     <t>software to assist in tracking all aspects of asbestos renovation and demolition activities and stationary source enforcement</t>
   </si>
   <si>
-    <t>Operational Funding/Software</t>
+    <t>Operational Funding, Software</t>
   </si>
   <si>
     <t>for Air Quality Program software to assist in tracking all aspects of asbestos renovation and demolition activities and stationary source enforcement; this will replace a series of spreadsheets and old software</t>
@@ -368,9 +368,6 @@
   </si>
   <si>
     <t>To update / develop software the Air Quality Program enforcement and permitting staff use</t>
-  </si>
-  <si>
-    <t>Operational Funding, Software</t>
   </si>
   <si>
     <t>Tree planting</t>
@@ -1172,6 +1169,9 @@
   </si>
   <si>
     <t>Project Category 2</t>
+  </si>
+  <si>
+    <t>Operational Funding/Software</t>
   </si>
   <si>
     <t>Software</t>
@@ -2706,7 +2706,7 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" spans="1:21" ht="33.950000000000003">
+    <row r="17" spans="1:21" ht="30.75">
       <c r="A17" s="11">
         <v>2018</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>109</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="F37" s="88" t="s">
         <v>35</v>
@@ -3509,7 +3509,7 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
     </row>
-    <row r="38" spans="1:21" ht="17.100000000000001">
+    <row r="38" spans="1:21">
       <c r="A38" s="11">
         <v>2020</v>
       </c>
@@ -3520,17 +3520,17 @@
         <v>59560</v>
       </c>
       <c r="D38" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="18" t="s">
         <v>111</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>112</v>
       </c>
       <c r="G38" s="18"/>
       <c r="H38" s="73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I38" s="11"/>
       <c r="J38" s="18"/>
@@ -3546,7 +3546,7 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" spans="1:21" ht="17.100000000000001">
+    <row r="39" spans="1:21">
       <c r="A39" s="11">
         <v>2020</v>
       </c>
@@ -3557,17 +3557,17 @@
         <v>98000</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G39" s="18"/>
       <c r="H39" s="73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39" s="11"/>
       <c r="J39" s="18"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G40" s="52"/>
       <c r="H40" s="70" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I40" s="11"/>
       <c r="J40" s="62" t="s">
@@ -3635,11 +3635,11 @@
         <v>62</v>
       </c>
       <c r="F41" s="89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G41" s="89"/>
       <c r="H41" s="111" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J41" s="108" t="s">
         <v>32</v>
@@ -3671,11 +3671,11 @@
         <v>41</v>
       </c>
       <c r="F42" s="81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G42" s="81"/>
       <c r="H42" s="82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I42" s="11"/>
       <c r="J42" s="81" t="s">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="G43" s="52"/>
       <c r="H43" s="70" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="62" t="s">
@@ -3735,25 +3735,25 @@
         <v>2020</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C44" s="2">
         <v>99995</v>
       </c>
       <c r="D44" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="20" t="s">
         <v>123</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>124</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="H44" s="76" t="s">
         <v>125</v>
-      </c>
-      <c r="H44" s="76" t="s">
-        <v>126</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>31</v>
@@ -3778,25 +3778,25 @@
         <v>2020</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C45" s="2">
         <v>15000</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F45" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G45" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="H45" s="77" t="s">
         <v>129</v>
-      </c>
-      <c r="H45" s="77" t="s">
-        <v>130</v>
       </c>
       <c r="J45" s="20" t="s">
         <v>60</v>
@@ -3818,25 +3818,25 @@
         <v>2020</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C46" s="2">
         <v>98000</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F46" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="G46" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="G46" s="19" t="s">
+      <c r="H46" s="76" t="s">
         <v>132</v>
-      </c>
-      <c r="H46" s="76" t="s">
-        <v>133</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="19"/>
@@ -3857,25 +3857,25 @@
         <v>2020</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C47" s="2">
         <v>500000</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E47" s="46" t="s">
         <v>34</v>
       </c>
       <c r="F47" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="G47" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="G47" s="46" t="s">
+      <c r="H47" s="75" t="s">
         <v>137</v>
-      </c>
-      <c r="H47" s="75" t="s">
-        <v>138</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="62" t="s">
@@ -3898,25 +3898,25 @@
         <v>2020</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C48" s="7">
         <v>55000</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E48" s="46" t="s">
         <v>34</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G48" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="H48" s="75" t="s">
         <v>141</v>
-      </c>
-      <c r="H48" s="75" t="s">
-        <v>142</v>
       </c>
       <c r="J48" s="62" t="s">
         <v>32</v>
@@ -3938,31 +3938,31 @@
         <v>2020</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="2">
         <v>75000</v>
       </c>
       <c r="D49" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E49" s="91" t="s">
         <v>88</v>
       </c>
       <c r="F49" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="G49" s="46" t="s">
+      <c r="H49" s="75" t="s">
         <v>146</v>
-      </c>
-      <c r="H49" s="75" t="s">
-        <v>147</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>31</v>
       </c>
       <c r="J49" s="52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -4003,31 +4003,31 @@
         <v>2020</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C50" s="2">
         <v>340554</v>
       </c>
       <c r="D50" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="F50" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="F50" s="45" t="s">
+      <c r="G50" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="46" t="s">
+      <c r="H50" s="75" t="s">
         <v>153</v>
-      </c>
-      <c r="H50" s="75" t="s">
-        <v>154</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>31</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -4041,30 +4041,30 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="1:43" ht="33.950000000000003">
+    <row r="51" spans="1:43" ht="30.75">
       <c r="A51" s="6">
         <v>2020</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C51" s="2">
         <v>548725</v>
       </c>
       <c r="D51" s="87" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" s="114" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="114" t="s">
         <v>157</v>
       </c>
-      <c r="E51" s="114" t="s">
-        <v>110</v>
-      </c>
-      <c r="F51" s="114" t="s">
+      <c r="G51" s="87" t="s">
         <v>158</v>
       </c>
-      <c r="G51" s="87" t="s">
+      <c r="H51" s="92" t="s">
         <v>159</v>
-      </c>
-      <c r="H51" s="92" t="s">
-        <v>160</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>31</v>
@@ -4087,28 +4087,28 @@
         <v>2021</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C52" s="7">
         <v>200000</v>
       </c>
       <c r="D52" s="90" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="E52" s="90" t="s">
+      <c r="F52" s="94" t="s">
         <v>162</v>
       </c>
-      <c r="F52" s="94" t="s">
+      <c r="G52" s="95" t="s">
         <v>163</v>
       </c>
-      <c r="G52" s="95" t="s">
+      <c r="H52" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="H52" s="96" t="s">
+      <c r="I52" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="J52" s="90"/>
       <c r="K52" s="1"/>
@@ -4120,29 +4120,29 @@
         <v>2021</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C53" s="4">
         <v>9941</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E53" s="39" t="s">
         <v>41</v>
       </c>
       <c r="F53" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="G53" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="G53" s="39" t="s">
+      <c r="H53" s="78" t="s">
         <v>170</v>
-      </c>
-      <c r="H53" s="78" t="s">
-        <v>171</v>
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -4183,29 +4183,29 @@
         <v>2021</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C54" s="4">
         <v>69956</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E54" s="39" t="s">
         <v>41</v>
       </c>
       <c r="F54" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="G54" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="G54" s="39" t="s">
+      <c r="H54" s="78" t="s">
         <v>174</v>
-      </c>
-      <c r="H54" s="78" t="s">
-        <v>175</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -4216,25 +4216,25 @@
         <v>2023</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C55" s="2">
         <v>9000</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E55" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="G55" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="H55" s="77" t="s">
         <v>178</v>
-      </c>
-      <c r="H55" s="77" t="s">
-        <v>179</v>
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="20"/>
@@ -4244,25 +4244,25 @@
         <v>2023</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C56" s="2">
         <v>750000</v>
       </c>
       <c r="D56" s="98" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E56" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F56" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="G56" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="G56" s="98" t="s">
+      <c r="H56" s="99" t="s">
         <v>183</v>
-      </c>
-      <c r="H56" s="99" t="s">
-        <v>184</v>
       </c>
       <c r="J56" s="98"/>
     </row>
@@ -4271,28 +4271,28 @@
         <v>2023</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="2">
         <v>700000</v>
       </c>
       <c r="D57" s="98" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E57" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F57" s="98" t="s">
+        <v>184</v>
+      </c>
+      <c r="G57" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="G57" s="98" t="s">
+      <c r="H57" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="H57" s="99" t="s">
+      <c r="J57" s="98" t="s">
         <v>187</v>
-      </c>
-      <c r="J57" s="98" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:43" ht="68.099999999999994">
@@ -4300,13 +4300,13 @@
         <v>2023</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C58" s="2">
         <v>46000</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>16</v>
@@ -4315,10 +4315,10 @@
         <v>17</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H58" s="76" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="19" t="s">
@@ -4330,13 +4330,13 @@
         <v>2023</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C59" s="2">
         <v>46000</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>16</v>
@@ -4345,10 +4345,10 @@
         <v>17</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H59" s="76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="19" t="s">
@@ -4360,28 +4360,28 @@
         <v>2023</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C60" s="2">
         <v>748339</v>
       </c>
       <c r="D60" s="100" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E60" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F60" s="98" t="s">
+        <v>192</v>
+      </c>
+      <c r="G60" s="98" t="s">
         <v>193</v>
       </c>
-      <c r="G60" s="98" t="s">
+      <c r="H60" s="99" t="s">
         <v>194</v>
       </c>
-      <c r="H60" s="99" t="s">
+      <c r="J60" s="98" t="s">
         <v>195</v>
-      </c>
-      <c r="J60" s="98" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:43" ht="51">
@@ -4389,29 +4389,29 @@
         <v>2024</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C61" s="2">
         <v>46000</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F61" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G61" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="G61" s="19" t="s">
+      <c r="H61" s="76" t="s">
         <v>200</v>
-      </c>
-      <c r="H61" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I61" s="6"/>
       <c r="J61" s="40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:43" ht="51">
@@ -4419,29 +4419,29 @@
         <v>2024</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C62" s="2">
         <v>46000</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H62" s="76" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:43" ht="51">
@@ -4449,28 +4449,28 @@
         <v>2024</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="98" t="s">
         <v>205</v>
-      </c>
-      <c r="D63" s="98" t="s">
-        <v>206</v>
       </c>
       <c r="E63" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F63" s="98" t="s">
+        <v>206</v>
+      </c>
+      <c r="G63" s="98" t="s">
+        <v>199</v>
+      </c>
+      <c r="H63" s="99" t="s">
         <v>207</v>
       </c>
-      <c r="G63" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="H63" s="99" t="s">
+      <c r="J63" s="98" t="s">
         <v>208</v>
-      </c>
-      <c r="J63" s="98" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:43" ht="51">
@@ -4478,28 +4478,28 @@
         <v>2024</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C64" s="2">
         <v>43272</v>
       </c>
       <c r="D64" s="98" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E64" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F64" s="98" t="s">
+        <v>210</v>
+      </c>
+      <c r="G64" s="98" t="s">
+        <v>199</v>
+      </c>
+      <c r="H64" s="99" t="s">
         <v>211</v>
       </c>
-      <c r="G64" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="H64" s="99" t="s">
+      <c r="J64" s="101" t="s">
         <v>212</v>
-      </c>
-      <c r="J64" s="101" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="51">
@@ -4507,28 +4507,28 @@
         <v>2024</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C65" s="2">
         <v>75000</v>
       </c>
       <c r="D65" s="98" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E65" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F65" s="98" t="s">
+        <v>213</v>
+      </c>
+      <c r="G65" s="98" t="s">
+        <v>199</v>
+      </c>
+      <c r="H65" s="99" t="s">
         <v>214</v>
       </c>
-      <c r="G65" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="H65" s="99" t="s">
+      <c r="J65" s="101" t="s">
         <v>215</v>
-      </c>
-      <c r="J65" s="101" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="51">
@@ -4536,28 +4536,28 @@
         <v>2024</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C66" s="2">
         <v>800000</v>
       </c>
       <c r="D66" s="98" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E66" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F66" s="98" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G66" s="98" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H66" s="99" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J66" s="101" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="51">
@@ -4565,28 +4565,28 @@
         <v>2024</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C67" s="2">
         <v>186789</v>
       </c>
       <c r="D67" s="98" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E67" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F67" s="98" t="s">
+        <v>219</v>
+      </c>
+      <c r="G67" s="98" t="s">
+        <v>199</v>
+      </c>
+      <c r="H67" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="G67" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="H67" s="99" t="s">
+      <c r="J67" s="101" t="s">
         <v>221</v>
-      </c>
-      <c r="J67" s="101" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="51">
@@ -4594,29 +4594,29 @@
         <v>2024</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C68" s="2">
         <v>997450</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E68" s="49" t="s">
         <v>46</v>
       </c>
       <c r="F68" s="49" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G68" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H68" s="79" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="51">
@@ -4624,29 +4624,29 @@
         <v>2024</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C69" s="2">
         <v>1000000</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E69" s="49" t="s">
         <v>46</v>
       </c>
       <c r="F69" s="49" t="s">
+        <v>225</v>
+      </c>
+      <c r="G69" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="H69" s="79" t="s">
         <v>226</v>
-      </c>
-      <c r="G69" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="H69" s="79" t="s">
-        <v>227</v>
       </c>
       <c r="I69" s="6"/>
       <c r="J69" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="51">
@@ -4654,31 +4654,31 @@
         <v>2024</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C70" s="2">
         <v>500000</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E70" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="F70" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="F70" s="19" t="s">
+      <c r="G70" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="H70" s="79" t="s">
         <v>230</v>
-      </c>
-      <c r="G70" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="H70" s="79" t="s">
-        <v>231</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J70" s="50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1">
@@ -6074,18 +6074,18 @@
         <v>2500</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -6100,18 +6100,18 @@
         <v>2500</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -6126,16 +6126,16 @@
         <v>184000</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -6150,16 +6150,16 @@
         <v>1140375</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J5" s="1"/>
     </row>
@@ -6174,18 +6174,18 @@
         <v>2500</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -6200,18 +6200,18 @@
         <v>25000</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J7" s="1"/>
     </row>
@@ -6226,7 +6226,7 @@
         <v>2500</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>71</v>
@@ -6235,7 +6235,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -6250,16 +6250,16 @@
         <v>300000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -6274,16 +6274,16 @@
         <v>30000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -6298,16 +6298,16 @@
         <v>80000</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J11" s="1"/>
     </row>
@@ -6322,7 +6322,7 @@
         <v>5000</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>71</v>
@@ -6331,7 +6331,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J12" s="1"/>
     </row>
@@ -6346,18 +6346,18 @@
         <v>1300000</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J13" s="1"/>
     </row>
@@ -6372,16 +6372,16 @@
         <v>44000</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J14" s="1"/>
     </row>
@@ -6396,7 +6396,7 @@
         <v>840000</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
@@ -6405,7 +6405,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -6431,7 +6431,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -6446,7 +6446,7 @@
         <v>32500</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
@@ -6455,7 +6455,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J17" s="1"/>
     </row>
@@ -6470,7 +6470,7 @@
         <v>20100</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -6496,7 +6496,7 @@
         <v>60000</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
@@ -6505,7 +6505,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -6520,16 +6520,16 @@
         <v>40000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J20" s="1"/>
     </row>
@@ -6544,7 +6544,7 @@
         <v>18000</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
@@ -6553,7 +6553,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J21" s="1"/>
     </row>
@@ -6568,14 +6568,14 @@
         <v>500000</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J22" s="1"/>
     </row>
@@ -6590,7 +6590,7 @@
         <v>20000</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
@@ -6599,7 +6599,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -6614,16 +6614,16 @@
         <v>25000</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J24" s="1"/>
     </row>
@@ -6638,16 +6638,16 @@
         <v>25000</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J25" s="1"/>
     </row>
@@ -6662,18 +6662,18 @@
         <v>2500</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J26" s="1"/>
     </row>
@@ -6688,7 +6688,7 @@
         <v>90000</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J27" s="1"/>
     </row>
@@ -6712,14 +6712,14 @@
         <v>10000</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J28" s="1"/>
     </row>
@@ -6734,14 +6734,14 @@
         <v>200000</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J29" s="1"/>
     </row>
@@ -6756,18 +6756,18 @@
         <v>2500</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J30" s="1"/>
     </row>
@@ -6782,7 +6782,7 @@
         <v>500000</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
@@ -6791,7 +6791,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J31" s="1"/>
     </row>
@@ -6806,14 +6806,14 @@
         <v>14000</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="23"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J32" s="1"/>
     </row>
@@ -6828,14 +6828,14 @@
         <v>150000</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="6"/>
       <c r="G33" s="23"/>
       <c r="H33" s="1"/>
       <c r="I33" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J33" s="1"/>
     </row>
@@ -6850,14 +6850,14 @@
         <v>25000</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J34" s="1"/>
     </row>
@@ -6872,16 +6872,16 @@
         <v>45000</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="1"/>
       <c r="I35" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J35" s="1"/>
     </row>
@@ -6896,7 +6896,7 @@
         <v>500000</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="6" t="s">
@@ -6905,7 +6905,7 @@
       <c r="G36" s="23"/>
       <c r="H36" s="1"/>
       <c r="I36" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J36" s="1"/>
     </row>
@@ -6920,18 +6920,18 @@
         <v>2500</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>71</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="1"/>
       <c r="I37" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J37" s="1"/>
     </row>
@@ -6946,14 +6946,14 @@
         <v>150000</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
       <c r="G38" s="23"/>
       <c r="H38" s="1"/>
       <c r="I38" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J38" s="1"/>
     </row>
@@ -6968,7 +6968,7 @@
         <v>100000</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="6" t="s">
@@ -6977,7 +6977,7 @@
       <c r="G39" s="23"/>
       <c r="H39" s="1"/>
       <c r="I39" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J39" s="1"/>
     </row>
@@ -6992,16 +6992,16 @@
         <v>2500</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E40" s="25"/>
       <c r="F40" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G40" s="23"/>
       <c r="H40" s="1"/>
       <c r="I40" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J40" s="1"/>
     </row>
@@ -7016,7 +7016,7 @@
         <v>10000</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E41" s="25" t="s">
         <v>71</v>
@@ -7025,7 +7025,7 @@
       <c r="G41" s="23"/>
       <c r="H41" s="1"/>
       <c r="I41" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J41" s="1"/>
     </row>
@@ -7040,14 +7040,14 @@
         <v>920000</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J42" s="1"/>
     </row>
@@ -7073,7 +7073,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J43" s="1"/>
     </row>
@@ -7088,16 +7088,16 @@
         <v>45000</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J44" s="1"/>
     </row>
@@ -7112,7 +7112,7 @@
         <v>180000</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="6" t="s">
@@ -7121,7 +7121,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J45" s="1"/>
     </row>
@@ -7136,14 +7136,14 @@
         <v>2250</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -7158,16 +7158,16 @@
         <v>860000</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -7182,7 +7182,7 @@
         <v>1000</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>71</v>
@@ -7191,7 +7191,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -7206,14 +7206,14 @@
         <v>2000</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="6"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J49" s="1"/>
     </row>
@@ -7228,10 +7228,10 @@
         <v>150000</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>329</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>35</v>
@@ -7239,7 +7239,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J50" s="1"/>
     </row>
@@ -7254,18 +7254,18 @@
         <v>3000</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J51" s="1"/>
     </row>
@@ -7280,18 +7280,18 @@
         <v>2500</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>71</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J52" s="1"/>
     </row>
@@ -7306,16 +7306,16 @@
         <v>12000</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J53" s="5"/>
     </row>
@@ -7330,7 +7330,7 @@
         <v>67000</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="11" t="s">
@@ -7339,7 +7339,7 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J54" s="5"/>
     </row>
@@ -7354,16 +7354,16 @@
         <v>75000</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J55" s="5"/>
     </row>
@@ -7378,14 +7378,14 @@
         <v>300000</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="11"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J56" s="5"/>
     </row>
@@ -7400,16 +7400,16 @@
         <v>300000</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J57" s="5"/>
     </row>
@@ -7424,18 +7424,18 @@
         <v>7500</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J58" s="5"/>
     </row>
@@ -7450,11 +7450,11 @@
         <v>24000</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -7474,16 +7474,16 @@
         <v>750000</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J60" s="5"/>
     </row>
@@ -7498,16 +7498,16 @@
         <v>9000</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J61" s="5"/>
     </row>
@@ -7529,7 +7529,7 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J62" s="5"/>
     </row>
@@ -7545,13 +7545,13 @@
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J63" s="5"/>
     </row>
@@ -7568,12 +7568,12 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J64" s="5"/>
     </row>
@@ -7595,7 +7595,7 @@
       <c r="G65" s="37"/>
       <c r="H65" s="37"/>
       <c r="I65" s="37" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J65" s="5"/>
     </row>
@@ -8451,10 +8451,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="115" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1" s="115" t="s">
         <v>361</v>
-      </c>
-      <c r="D1" s="115" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.100000000000001">
@@ -8662,7 +8662,7 @@
         <v>45000</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>73</v>
+        <v>362</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -8771,7 +8771,7 @@
         <v>34</v>
       </c>
       <c r="D25" s="119" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25" s="5"/>
     </row>
@@ -8941,7 +8941,7 @@
         <v>59560</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -8954,7 +8954,7 @@
         <v>98000</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
@@ -9271,7 +9271,7 @@
         <v>2024</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>53</v>

--- a/1740CAF.xlsx
+++ b/1740CAF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lan74_pitt_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{679645A4-519C-42B3-89C6-BF342277225F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7755439-CB61-4FBC-9BB8-CA30122B8809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="760" windowWidth="23260" windowHeight="16260" firstSheet="2" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
+    <workbookView xWindow="5540" yWindow="760" windowWidth="23260" windowHeight="16260" xr2:uid="{C5E92D08-1D1E-B946-9078-11755ACCCC10}"/>
   </bookViews>
   <sheets>
     <sheet name="2015-Present" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
     <t>air pollution public education projects and emission reduction projects</t>
   </si>
   <si>
-    <t>Public Communication, Emission Reduction</t>
+    <t>Public Communications, Emission Reduction</t>
   </si>
   <si>
     <t>to fund small projects ($10k - $30k) addressing air pollution public education projects and emission reduction projects, with $150,000 going to each of the two categories</t>
@@ -304,7 +304,7 @@
     <t>for the Air Quality Program to run a half-day workshop for municipal officials on air quality topics</t>
   </si>
   <si>
-    <t>Operational Funding, Public Communication</t>
+    <t>Operational Funding, Public Communications</t>
   </si>
   <si>
     <t>To provide professional and technical support on an as-needed basis to the Air Quality Program for case analysis, data and technical support, legal support, and medical and toxicology consulting</t>
@@ -521,9 +521,6 @@
   </si>
   <si>
     <t>Air Ambassador Program</t>
-  </si>
-  <si>
-    <t>Public Communication</t>
   </si>
   <si>
     <t>Various</t>
@@ -1172,6 +1169,9 @@
   </si>
   <si>
     <t>Operational Funding/Software</t>
+  </si>
+  <si>
+    <t>Public Communication</t>
   </si>
   <si>
     <t>Software</t>
@@ -2744,7 +2744,7 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" spans="1:21" ht="33.950000000000003">
+    <row r="18" spans="1:21">
       <c r="A18" s="11">
         <v>2018</v>
       </c>
@@ -3009,7 +3009,7 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="1:21" ht="33.950000000000003">
+    <row r="25" spans="1:21" ht="30.75">
       <c r="A25" s="11">
         <v>2019</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="1:43" s="83" customFormat="1" ht="51">
+    <row r="49" spans="1:43" s="83" customFormat="1" ht="46.5">
       <c r="A49" s="6">
         <v>2020</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="1:43" ht="33.950000000000003">
+    <row r="52" spans="1:43" ht="30.75">
       <c r="A52" s="6">
         <v>2021</v>
       </c>
@@ -4096,19 +4096,19 @@
         <v>160</v>
       </c>
       <c r="E52" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="94" t="s">
         <v>161</v>
       </c>
-      <c r="F52" s="94" t="s">
+      <c r="G52" s="95" t="s">
         <v>162</v>
       </c>
-      <c r="G52" s="95" t="s">
+      <c r="H52" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="96" t="s">
+      <c r="I52" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="J52" s="90"/>
       <c r="K52" s="1"/>
@@ -4120,25 +4120,25 @@
         <v>2021</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C53" s="4">
         <v>9941</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E53" s="39" t="s">
         <v>41</v>
       </c>
       <c r="F53" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="G53" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="G53" s="39" t="s">
+      <c r="H53" s="78" t="s">
         <v>169</v>
-      </c>
-      <c r="H53" s="78" t="s">
-        <v>170</v>
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="45" t="s">
@@ -4189,19 +4189,19 @@
         <v>69956</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E54" s="39" t="s">
         <v>41</v>
       </c>
       <c r="F54" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="G54" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="G54" s="39" t="s">
+      <c r="H54" s="78" t="s">
         <v>173</v>
-      </c>
-      <c r="H54" s="78" t="s">
-        <v>174</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="45" t="s">
@@ -4216,7 +4216,7 @@
         <v>2023</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C55" s="2">
         <v>9000</v>
@@ -4228,13 +4228,13 @@
         <v>11</v>
       </c>
       <c r="F55" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G55" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="H55" s="77" t="s">
         <v>177</v>
-      </c>
-      <c r="H55" s="77" t="s">
-        <v>178</v>
       </c>
       <c r="I55" s="6"/>
       <c r="J55" s="20"/>
@@ -4244,25 +4244,25 @@
         <v>2023</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C56" s="2">
         <v>750000</v>
       </c>
       <c r="D56" s="98" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E56" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F56" s="98" t="s">
+        <v>180</v>
+      </c>
+      <c r="G56" s="98" t="s">
         <v>181</v>
       </c>
-      <c r="G56" s="98" t="s">
+      <c r="H56" s="99" t="s">
         <v>182</v>
-      </c>
-      <c r="H56" s="99" t="s">
-        <v>183</v>
       </c>
       <c r="J56" s="98"/>
     </row>
@@ -4271,28 +4271,28 @@
         <v>2023</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C57" s="2">
         <v>700000</v>
       </c>
       <c r="D57" s="98" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E57" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F57" s="98" t="s">
+        <v>183</v>
+      </c>
+      <c r="G57" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="G57" s="98" t="s">
+      <c r="H57" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="H57" s="99" t="s">
+      <c r="J57" s="98" t="s">
         <v>186</v>
-      </c>
-      <c r="J57" s="98" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:43" ht="68.099999999999994">
@@ -4300,13 +4300,13 @@
         <v>2023</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C58" s="2">
         <v>46000</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>16</v>
@@ -4315,10 +4315,10 @@
         <v>17</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H58" s="76" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="19" t="s">
@@ -4330,13 +4330,13 @@
         <v>2023</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2">
         <v>46000</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>16</v>
@@ -4345,10 +4345,10 @@
         <v>17</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H59" s="76" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="19" t="s">
@@ -4360,28 +4360,28 @@
         <v>2023</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C60" s="2">
         <v>748339</v>
       </c>
       <c r="D60" s="100" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E60" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F60" s="98" t="s">
+        <v>191</v>
+      </c>
+      <c r="G60" s="98" t="s">
         <v>192</v>
       </c>
-      <c r="G60" s="98" t="s">
+      <c r="H60" s="99" t="s">
         <v>193</v>
       </c>
-      <c r="H60" s="99" t="s">
+      <c r="J60" s="98" t="s">
         <v>194</v>
-      </c>
-      <c r="J60" s="98" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:43" ht="51">
@@ -4389,29 +4389,29 @@
         <v>2024</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C61" s="2">
         <v>46000</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F61" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="G61" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G61" s="19" t="s">
+      <c r="H61" s="76" t="s">
         <v>199</v>
-      </c>
-      <c r="H61" s="76" t="s">
-        <v>200</v>
       </c>
       <c r="I61" s="6"/>
       <c r="J61" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:43" ht="51">
@@ -4419,13 +4419,13 @@
         <v>2024</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C62" s="2">
         <v>46000</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>16</v>
@@ -4434,10 +4434,10 @@
         <v>130</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H62" s="76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="40" t="s">
@@ -4449,28 +4449,28 @@
         <v>2024</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="98" t="s">
         <v>204</v>
-      </c>
-      <c r="D63" s="98" t="s">
-        <v>205</v>
       </c>
       <c r="E63" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F63" s="98" t="s">
+        <v>205</v>
+      </c>
+      <c r="G63" s="98" t="s">
+        <v>198</v>
+      </c>
+      <c r="H63" s="99" t="s">
         <v>206</v>
       </c>
-      <c r="G63" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="H63" s="99" t="s">
+      <c r="J63" s="98" t="s">
         <v>207</v>
-      </c>
-      <c r="J63" s="98" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:43" ht="51">
@@ -4478,28 +4478,28 @@
         <v>2024</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C64" s="2">
         <v>43272</v>
       </c>
       <c r="D64" s="98" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E64" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F64" s="98" t="s">
+        <v>209</v>
+      </c>
+      <c r="G64" s="98" t="s">
+        <v>198</v>
+      </c>
+      <c r="H64" s="99" t="s">
         <v>210</v>
       </c>
-      <c r="G64" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="H64" s="99" t="s">
+      <c r="J64" s="101" t="s">
         <v>211</v>
-      </c>
-      <c r="J64" s="101" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="51">
@@ -4507,28 +4507,28 @@
         <v>2024</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C65" s="2">
         <v>75000</v>
       </c>
       <c r="D65" s="98" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E65" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F65" s="98" t="s">
+        <v>212</v>
+      </c>
+      <c r="G65" s="98" t="s">
+        <v>198</v>
+      </c>
+      <c r="H65" s="99" t="s">
         <v>213</v>
       </c>
-      <c r="G65" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="H65" s="99" t="s">
+      <c r="J65" s="101" t="s">
         <v>214</v>
-      </c>
-      <c r="J65" s="101" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="51">
@@ -4536,28 +4536,28 @@
         <v>2024</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C66" s="2">
         <v>800000</v>
       </c>
       <c r="D66" s="98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E66" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F66" s="98" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G66" s="98" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H66" s="99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J66" s="101" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="51">
@@ -4565,28 +4565,28 @@
         <v>2024</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C67" s="2">
         <v>186789</v>
       </c>
       <c r="D67" s="98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E67" s="112" t="s">
         <v>53</v>
       </c>
       <c r="F67" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="G67" s="98" t="s">
+        <v>198</v>
+      </c>
+      <c r="H67" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="G67" s="98" t="s">
-        <v>199</v>
-      </c>
-      <c r="H67" s="99" t="s">
+      <c r="J67" s="101" t="s">
         <v>220</v>
-      </c>
-      <c r="J67" s="101" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="51">
@@ -4594,29 +4594,29 @@
         <v>2024</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C68" s="2">
         <v>997450</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E68" s="49" t="s">
         <v>46</v>
       </c>
       <c r="F68" s="49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G68" s="49" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H68" s="79" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="51">
@@ -4624,29 +4624,29 @@
         <v>2024</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C69" s="2">
         <v>1000000</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E69" s="49" t="s">
         <v>46</v>
       </c>
       <c r="F69" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="G69" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="H69" s="79" t="s">
         <v>225</v>
-      </c>
-      <c r="G69" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="H69" s="79" t="s">
-        <v>226</v>
       </c>
       <c r="I69" s="6"/>
       <c r="J69" s="50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="51">
@@ -4654,31 +4654,31 @@
         <v>2024</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C70" s="2">
         <v>500000</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E70" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F70" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="F70" s="19" t="s">
+      <c r="G70" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="79" t="s">
         <v>229</v>
-      </c>
-      <c r="G70" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="H70" s="79" t="s">
-        <v>230</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J70" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1">
@@ -6074,18 +6074,18 @@
         <v>2500</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -6100,18 +6100,18 @@
         <v>2500</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -6126,16 +6126,16 @@
         <v>184000</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -6150,16 +6150,16 @@
         <v>1140375</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J5" s="1"/>
     </row>
@@ -6174,18 +6174,18 @@
         <v>2500</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -6200,18 +6200,18 @@
         <v>25000</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J7" s="1"/>
     </row>
@@ -6226,7 +6226,7 @@
         <v>2500</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>71</v>
@@ -6235,7 +6235,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -6250,7 +6250,7 @@
         <v>300000</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
@@ -6259,7 +6259,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -6283,7 +6283,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -6298,7 +6298,7 @@
         <v>80000</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
@@ -6307,7 +6307,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J11" s="1"/>
     </row>
@@ -6322,7 +6322,7 @@
         <v>5000</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>71</v>
@@ -6331,7 +6331,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J12" s="1"/>
     </row>
@@ -6346,18 +6346,18 @@
         <v>1300000</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J13" s="1"/>
     </row>
@@ -6372,16 +6372,16 @@
         <v>44000</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J14" s="1"/>
     </row>
@@ -6396,7 +6396,7 @@
         <v>840000</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
@@ -6405,7 +6405,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J15" s="1"/>
     </row>
@@ -6431,7 +6431,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -6446,7 +6446,7 @@
         <v>32500</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
@@ -6455,7 +6455,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J17" s="1"/>
     </row>
@@ -6470,7 +6470,7 @@
         <v>20100</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -6496,7 +6496,7 @@
         <v>60000</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
@@ -6505,7 +6505,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -6520,16 +6520,16 @@
         <v>40000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J20" s="1"/>
     </row>
@@ -6544,7 +6544,7 @@
         <v>18000</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
@@ -6553,7 +6553,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J21" s="1"/>
     </row>
@@ -6568,14 +6568,14 @@
         <v>500000</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J22" s="1"/>
     </row>
@@ -6590,7 +6590,7 @@
         <v>20000</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
@@ -6599,7 +6599,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -6614,16 +6614,16 @@
         <v>25000</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J24" s="1"/>
     </row>
@@ -6638,16 +6638,16 @@
         <v>25000</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J25" s="1"/>
     </row>
@@ -6662,18 +6662,18 @@
         <v>2500</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J26" s="1"/>
     </row>
@@ -6688,7 +6688,7 @@
         <v>90000</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J27" s="1"/>
     </row>
@@ -6712,14 +6712,14 @@
         <v>10000</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J28" s="1"/>
     </row>
@@ -6734,14 +6734,14 @@
         <v>200000</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J29" s="1"/>
     </row>
@@ -6756,18 +6756,18 @@
         <v>2500</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J30" s="1"/>
     </row>
@@ -6782,7 +6782,7 @@
         <v>500000</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
@@ -6791,7 +6791,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J31" s="1"/>
     </row>
@@ -6806,14 +6806,14 @@
         <v>14000</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="23"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J32" s="1"/>
     </row>
@@ -6828,14 +6828,14 @@
         <v>150000</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="6"/>
       <c r="G33" s="23"/>
       <c r="H33" s="1"/>
       <c r="I33" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J33" s="1"/>
     </row>
@@ -6850,14 +6850,14 @@
         <v>25000</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J34" s="1"/>
     </row>
@@ -6872,16 +6872,16 @@
         <v>45000</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="1"/>
       <c r="I35" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J35" s="1"/>
     </row>
@@ -6896,7 +6896,7 @@
         <v>500000</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="6" t="s">
@@ -6905,7 +6905,7 @@
       <c r="G36" s="23"/>
       <c r="H36" s="1"/>
       <c r="I36" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J36" s="1"/>
     </row>
@@ -6920,18 +6920,18 @@
         <v>2500</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>71</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G37" s="23"/>
       <c r="H37" s="1"/>
       <c r="I37" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J37" s="1"/>
     </row>
@@ -6946,14 +6946,14 @@
         <v>150000</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="6"/>
       <c r="G38" s="23"/>
       <c r="H38" s="1"/>
       <c r="I38" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J38" s="1"/>
     </row>
@@ -6968,7 +6968,7 @@
         <v>100000</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="6" t="s">
@@ -6977,7 +6977,7 @@
       <c r="G39" s="23"/>
       <c r="H39" s="1"/>
       <c r="I39" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J39" s="1"/>
     </row>
@@ -6992,16 +6992,16 @@
         <v>2500</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E40" s="25"/>
       <c r="F40" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G40" s="23"/>
       <c r="H40" s="1"/>
       <c r="I40" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J40" s="1"/>
     </row>
@@ -7016,7 +7016,7 @@
         <v>10000</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E41" s="25" t="s">
         <v>71</v>
@@ -7025,7 +7025,7 @@
       <c r="G41" s="23"/>
       <c r="H41" s="1"/>
       <c r="I41" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J41" s="1"/>
     </row>
@@ -7040,14 +7040,14 @@
         <v>920000</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J42" s="1"/>
     </row>
@@ -7073,7 +7073,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J43" s="1"/>
     </row>
@@ -7088,16 +7088,16 @@
         <v>45000</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J44" s="1"/>
     </row>
@@ -7112,7 +7112,7 @@
         <v>180000</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="6" t="s">
@@ -7121,7 +7121,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J45" s="1"/>
     </row>
@@ -7136,14 +7136,14 @@
         <v>2250</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J46" s="1"/>
     </row>
@@ -7158,16 +7158,16 @@
         <v>860000</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J47" s="1"/>
     </row>
@@ -7182,7 +7182,7 @@
         <v>1000</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>71</v>
@@ -7191,7 +7191,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J48" s="1"/>
     </row>
@@ -7206,14 +7206,14 @@
         <v>2000</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="6"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J49" s="1"/>
     </row>
@@ -7228,10 +7228,10 @@
         <v>150000</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>35</v>
@@ -7239,7 +7239,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J50" s="1"/>
     </row>
@@ -7254,18 +7254,18 @@
         <v>3000</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J51" s="1"/>
     </row>
@@ -7286,12 +7286,12 @@
         <v>71</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J52" s="1"/>
     </row>
@@ -7306,16 +7306,16 @@
         <v>12000</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J53" s="5"/>
     </row>
@@ -7330,7 +7330,7 @@
         <v>67000</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="11" t="s">
@@ -7339,7 +7339,7 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J54" s="5"/>
     </row>
@@ -7354,7 +7354,7 @@
         <v>75000</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="11" t="s">
@@ -7363,7 +7363,7 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J55" s="5"/>
     </row>
@@ -7378,14 +7378,14 @@
         <v>300000</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="11"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J56" s="5"/>
     </row>
@@ -7400,16 +7400,16 @@
         <v>300000</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J57" s="5"/>
     </row>
@@ -7435,7 +7435,7 @@
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J58" s="5"/>
     </row>
@@ -7450,11 +7450,11 @@
         <v>24000</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -7474,16 +7474,16 @@
         <v>750000</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J60" s="5"/>
     </row>
@@ -7498,7 +7498,7 @@
         <v>9000</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="11" t="s">
@@ -7507,7 +7507,7 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J61" s="5"/>
     </row>
@@ -7529,7 +7529,7 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J62" s="5"/>
     </row>
@@ -7545,13 +7545,13 @@
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J63" s="5"/>
     </row>
@@ -7573,7 +7573,7 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J64" s="5"/>
     </row>
@@ -7595,7 +7595,7 @@
       <c r="G65" s="37"/>
       <c r="H65" s="37"/>
       <c r="I65" s="37" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J65" s="5"/>
     </row>
@@ -8451,10 +8451,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" s="115" t="s">
         <v>360</v>
-      </c>
-      <c r="D1" s="115" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.100000000000001">
@@ -8662,7 +8662,7 @@
         <v>45000</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -8771,7 +8771,7 @@
         <v>34</v>
       </c>
       <c r="D25" s="119" t="s">
-        <v>161</v>
+        <v>362</v>
       </c>
       <c r="E25" s="5"/>
     </row>
@@ -9271,7 +9271,7 @@
         <v>2024</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>53</v>
